--- a/outputs/aws-privesc-verification-20261022/aws-technique-verification.xlsx
+++ b/outputs/aws-privesc-verification-20261022/aws-technique-verification.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS techniques" sheetId="1" r:id="R7e09997ee17c4826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AWS techniques" sheetId="1" r:id="Rbf46c36a21d84767"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -75,16 +75,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AwsTechniqueVerification" displayName="AwsTechniqueVerification" ref="A1:H212" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AwsTechniqueVerification" displayName="AwsTechniqueVerification" ref="A1:O212" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="15">
     <x:tableColumn id="1" name="id"/>
     <x:tableColumn id="2" name="service"/>
     <x:tableColumn id="3" name="catalog_review"/>
     <x:tableColumn id="4" name="external_proof_route"/>
     <x:tableColumn id="5" name="proof_route"/>
     <x:tableColumn id="6" name="named_test_file"/>
-    <x:tableColumn id="7" name="end_to_end_suite"/>
-    <x:tableColumn id="8" name="remaining_work"/>
+    <x:tableColumn id="7" name="literal_test_file"/>
+    <x:tableColumn id="8" name="located_test_file"/>
+    <x:tableColumn id="9" name="focused_helper_test"/>
+    <x:tableColumn id="10" name="focused_helper_result"/>
+    <x:tableColumn id="11" name="isolated_graph_test"/>
+    <x:tableColumn id="12" name="isolated_graph_result"/>
+    <x:tableColumn id="13" name="end_to_end_suite"/>
+    <x:tableColumn id="14" name="work_done"/>
+    <x:tableColumn id="15" name="remaining_work"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -291,8 +298,15 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="66" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="92" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="66" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="66" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="62" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="70" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="92" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="92" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -315,9 +329,30 @@
         <x:v>named_test_file</x:v>
       </x:c>
       <x:c r="G1" s="5" t="str">
+        <x:v>literal_test_file</x:v>
+      </x:c>
+      <x:c r="H1" s="5" t="str">
+        <x:v>located_test_file</x:v>
+      </x:c>
+      <x:c r="I1" s="5" t="str">
+        <x:v>focused_helper_test</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="str">
+        <x:v>focused_helper_result</x:v>
+      </x:c>
+      <x:c r="K1" s="5" t="str">
+        <x:v>isolated_graph_test</x:v>
+      </x:c>
+      <x:c r="L1" s="5" t="str">
+        <x:v>isolated_graph_result</x:v>
+      </x:c>
+      <x:c r="M1" s="5" t="str">
         <x:v>end_to_end_suite</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="N1" s="5" t="str">
+        <x:v>work_done</x:v>
+      </x:c>
+      <x:c r="O1" s="5" t="str">
         <x:v>remaining_work</x:v>
       </x:c>
     </x:row>
@@ -339,10 +374,27 @@
       </x:c>
       <x:c r="F2" s="6" t="str"/>
       <x:c r="G2" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_amplify_role_routes.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_amplify_role_routes.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str"/>
+      <x:c r="L2" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="str">
+        <x:v>Current audit: PassRole to amplify.amazonaws.com, exact app UpdateApp, connected repository, branch inventory and StartJob on the same branch remain required. A concrete edge additionally needs fresh reviewed evidence that effective controlled build or backend commands actually performed a useful action under the exact service role, unavailable directly to the caller; app buildSpec alone does not prove that repository amplify.yml was overridden or that build commands used service-role credentials. Missing, wrong-branch, duplicate, stale and direct-caller proofs stay unresolved. Multiple-branch positive/negative tests and historical binding pass. AWS Amplify service-role, build settings and StartJob docs.</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -363,10 +415,27 @@
       </x:c>
       <x:c r="F3" s="6" t="str"/>
       <x:c r="G3" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_amplify_role_routes.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_amplify_role_routes.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str"/>
+      <x:c r="J3" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str"/>
+      <x:c r="L3" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M3" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="str">
+        <x:v>Current audit: PassRole, UpdateApp on a collected SSR app and a branch without another compute-role override remain required. A concrete edge needs fresh reviewed evidence that source-controlled deployed SSR code received an HTTP request and performed a useful action under the exact compute role, unavailable directly to the caller. Missing, wrong-branch, duplicate, stale and direct-caller proofs stay unresolved. Later-branch positive and negative tests and historical binding pass. AWS Amplify SSR compute-role documentation.</x:v>
+      </x:c>
+      <x:c r="O3" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -387,10 +456,27 @@
         <x:v>tests/test_peaso_privesc_facts_followups.py</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_facts_followups.py</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_facts_followups.py</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str"/>
+      <x:c r="J4" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str"/>
+      <x:c r="L4" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M4" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N4" s="6" t="str">
+        <x:v>CreateToken takes known AppId and returns one-time challenge without GetApp; exact app, partition, account, Region, collected Gen 1 backend environment and distinct backend-path authorization checked; token-only, app-ARN-only and other-app grants do not become supported paths, while token-only remains unresolved; Studio sign-in remains conditional; tests/test_peaso_privesc_facts_followups.py; AWS Amplify Admin UI CreateToken API, Amplify Admin Service Authorization Reference and Amplify Studio overview</x:v>
+      </x:c>
+      <x:c r="O4" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -411,10 +497,27 @@
         <x:v>tests/test_peaso_privesc_apprunner_existing_role.py</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_apprunner_existing_role.py</x:v>
       </x:c>
       <x:c r="H5" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_apprunner_existing_role.py</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str"/>
+      <x:c r="J5" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str"/>
+      <x:c r="L5" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M5" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N5" s="6" t="str">
+        <x:v>Collected RUNNING App Runner service must name the exact instance role, same-account private ECR image tag and AutoDeploymentsEnabled true; repository URI, ARN, tag mutability and all ECR token, layer upload and PutImage grants must join. Immutable tags require effective PutImageTagMutability; missing exclusion filters return unknown. Positive, wrong role, no auto deployment, immutable, wrong repository and missing PutImage negatives in tests/test_peaso_privesc_apprunner_existing_role.py; focused precondition test and direct evaluator positive/negative passed. A follow-up corrected ecr:GetAuthorizationToken to require a global Resource grant; repository-scoped token permission no longer produces a role edge. AWS App Runner deployment, ECR Service Authorization Reference and ECR push/mutability docs.</x:v>
+      </x:c>
+      <x:c r="O5" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -434,11 +537,26 @@
       <x:c r="F6" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G6" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G6" s="6" t="str"/>
       <x:c r="H6" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str"/>
+      <x:c r="J6" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str"/>
+      <x:c r="L6" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M6" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="str">
+        <x:v>Existing customer eligibility, CreateService, exact role PassRole with iam:PassedToService apprunner.amazonaws.com, and role trust to tasks.apprunner.amazonaws.com checked; wrong PassedToService and unproven customer negatives; tests/test_peaso_privesc_schema_ext.py; AWS App Runner CreateService, IAM guide, and AWSAppRunnerFullAccess policy</x:v>
+      </x:c>
+      <x:c r="O6" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -461,10 +579,27 @@
         <x:v>tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_schema_v3_aws.py, tests/test_peaso_privesc_v4_all_id_proofs.py, tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_v3_aws.py, tests/test_peaso_privesc_v4_all_id_proofs.py, tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str"/>
+      <x:c r="J7" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str"/>
+      <x:c r="L7" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M7" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="str">
+        <x:v>DescribeService exact service/name/id ARN, same partition/account/Region, exact IAM user subject and reviewed successful credential read/authentication checked; named action/resource denied to source and allowed with target key required; missing, false, conflicting, empty and cross-scope evidence negatives; tests/test_peaso_privesc_v4_exact_user_credentials.py and test_peaso_privesc_v4_all_id_proofs.py; AWS App Runner DescribeService API and Service Authorization Reference</x:v>
+      </x:c>
+      <x:c r="O7" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -485,10 +620,27 @@
         <x:v>tests/test_peaso_privesc_apprunner_existing_role.py</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_apprunner_existing_role.py</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_apprunner_existing_role.py</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str"/>
+      <x:c r="L8" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M8" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N8" s="6" t="str">
+        <x:v>Existing RUNNING image service, exact recorded InstanceRoleArn, service ARN and UpdateService grant; wrong role, Region, state, source type and permission negatives; tests/test_peaso_privesc_apprunner_existing_role.py; AWS UpdateService and DescribeService APIs.</x:v>
+      </x:c>
+      <x:c r="O8" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -508,11 +660,26 @@
       <x:c r="F9" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G9" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G9" s="6" t="str"/>
       <x:c r="H9" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str"/>
+      <x:c r="L9" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M9" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N9" s="6" t="str">
+        <x:v>Image-based RUNNING or recoverable CREATE_FAILED service, exact Region/account service ARN and UpdateService permission, role trust to tasks.apprunner.amazonaws.com, and PassRole with iam:PassedToService apprunner.amazonaws.com checked; wrong region, wrong service, wrong context, and unusable state negatives; tests/test_peaso_privesc_schema_ext.py; AWS App Runner UpdateService and Service APIs</x:v>
+      </x:c>
+      <x:c r="O9" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -533,10 +700,27 @@
         <x:v>tests/test_peaso_privesc_appstream_existing_builders.py</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_appstream_existing_builders.py</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_appstream_existing_builders.py</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K10" s="6" t="str"/>
+      <x:c r="L10" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M10" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N10" s="6" t="str">
+        <x:v>Exact RUNNING app block builder ARN, recorded IamRoleArn, and builder-scoped streaming URL permission joined in AWS evaluator; positive and wrong-builder/stopped/wrong-role/denied-inventory negatives in tests/test_peaso_privesc_appstream_existing_builders.py; AWS AppStream builder API and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O10" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -557,10 +741,27 @@
         <x:v>tests/test_peaso_privesc_appstream_existing_builders.py</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_appstream_existing_builders.py</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_appstream_existing_builders.py</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="str"/>
+      <x:c r="L11" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M11" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N11" s="6" t="str">
+        <x:v>Exact RUNNING image builder ARN, recorded IamRoleArn, and builder-scoped streaming URL permission joined in AWS evaluator; positive and wrong-builder/stopped/wrong-role/denied-inventory negatives in tests/test_peaso_privesc_appstream_existing_builders.py; AWS AppStream builder API and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O11" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -581,10 +782,27 @@
         <x:v>tests/test_peaso_privesc_appstream_existing_fleet.py</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_appstream_existing_fleet.py</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_appstream_existing_fleet.py</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="str"/>
+      <x:c r="L12" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M12" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N12" s="6" t="str">
+        <x:v>Exact running DESKTOP fleet ARN, recorded IamRoleArn, available capacity, collected associated stack, and fleet-scoped CreateStreamingURL joined in the AWS evaluator; positive and wrong-role/wrong-fleet/APP/stopped/no-capacity/denied-inventory negatives in tests/test_peaso_privesc_appstream_existing_fleet.py; AWS CreateStreamingURL, Fleet, and machine-role documentation.</x:v>
+      </x:c>
+      <x:c r="O12" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -605,10 +823,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="str"/>
+      <x:c r="L13" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M13" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N13" s="6" t="str">
+        <x:v>Builder creation, two-AZ network, app block association, start and streaming permissions. A follow-up requires CreateAppBlock on global Resource scope; a grant limited to one app-block ARN no longer yields the role edge. tests/test_peaso_privesc_aws_followups.py; AWS CreateAppBlockBuilder API and AppStream Service Authorization Reference</x:v>
+      </x:c>
+      <x:c r="O13" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -629,10 +864,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="str"/>
+      <x:c r="L14" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M14" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N14" s="6" t="str">
+        <x:v>Image readiness, builder creation, and matching streaming URL permissions; tests/test_peaso_privesc_aws_followups.py; AWS CreateImageBuilder API</x:v>
+      </x:c>
+      <x:c r="O14" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -653,10 +905,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H15" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str"/>
+      <x:c r="J15" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K15" s="6" t="str"/>
+      <x:c r="L15" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M15" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N15" s="6" t="str">
+        <x:v>Fleet image, stack association, PassRole trust, and fleet plus stack streaming URL permissions; tests/test_peaso_privesc_aws_followups.py; AWS AppStream API and Service Authorization Reference</x:v>
+      </x:c>
+      <x:c r="O15" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -677,10 +946,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="str"/>
+      <x:c r="L16" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M16" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N16" s="6" t="str">
+        <x:v>Builder state, role update, app block association, start and streaming permissions; tests/test_peaso_privesc_aws_followups.py; AWS UpdateAppBlockBuilder API</x:v>
+      </x:c>
+      <x:c r="O16" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -701,10 +987,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str"/>
+      <x:c r="J17" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="str"/>
+      <x:c r="L17" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M17" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N17" s="6" t="str">
+        <x:v>Stopped or stoppable fleet, role update, associated stack, and fleet plus stack streaming URL permissions; tests/test_peaso_privesc_aws_followups.py; AWS UpdateFleet API and Service Authorization Reference</x:v>
+      </x:c>
+      <x:c r="O17" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -725,10 +1028,27 @@
         <x:v>tests/test_peaso_privesc_appsync_new_api.py</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_appsync_new_api.py</x:v>
       </x:c>
       <x:c r="H18" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_appsync_new_api.py</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str"/>
+      <x:c r="J18" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="str"/>
+      <x:c r="L18" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M18" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N18" s="6" t="str">
+        <x:v>All five AppSync setup actions require effective global resource authorization, exact iam:PassRole with PassedToService appsync.amazonaws.com, and target role trust. Missing action, scoped-only resource, wrong service condition and wrong trust negatives in tests/test_peaso_privesc_appsync_new_api.py; AWS AppSync API and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O18" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -749,10 +1069,27 @@
         <x:v>tests/test_peaso_privesc_athena_sessions.py</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_athena_sessions.py</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_athena_sessions.py</x:v>
+      </x:c>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="str"/>
+      <x:c r="L19" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M19" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N19" s="6" t="str">
+        <x:v>Active PySpark 3 notebook session joined to exact GetSession execution role and NotebookVersion; CreatePresignedNotebookUrl on containing workgroup; wrong engine or no notebook negative; tests/test_peaso_privesc_athena_sessions.py; AWS CreatePresignedNotebookUrl and Spark API support.</x:v>
+      </x:c>
+      <x:c r="O19" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -773,10 +1110,27 @@
         <x:v>tests/test_peaso_privesc_athena_sessions.py</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_athena_sessions.py</x:v>
       </x:c>
       <x:c r="H20" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_athena_sessions.py</x:v>
+      </x:c>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K20" s="6" t="str"/>
+      <x:c r="L20" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M20" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N20" s="6" t="str">
+        <x:v>Active Apache Spark 3.5 session joined to exact GetSession execution role; GetSessionEndpoint on its workgroup and session ARNs; wrong engine/state/session grant negatives; tests/test_peaso_privesc_athena_sessions.py; AWS Spark Connect and Athena Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O20" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -797,10 +1151,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H21" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K21" s="6" t="str"/>
+      <x:c r="L21" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M21" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N21" s="6" t="str">
+        <x:v>One valid-region, free Athena workgroup name must satisfy CreateWorkGroup, StartSession and StartCalculationExecution together; collected workgroup inventory prevents an occupied-name edge and missing inventory leaves it unresolved. Target role must trust Athena and PassRole must allow the same workgroup through iam:AssociatedResourceArn and iam:PassedToService. Disjoint actions, occupied names, wrong association, invalid Region and wildcard-name replacement have focused positives/negatives. Spark engine compatibility and execution remain conditional; tests/test_peaso_privesc_aws_followups.py; AWS Athena CreateWorkGroup, StartSession, StartCalculationExecution, Spark migration and IAM condition-key docs.</x:v>
+      </x:c>
+      <x:c r="O21" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -821,10 +1192,27 @@
         <x:v>tests/test_peaso_privesc_athena_sessions.py</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_athena_sessions.py, tests/test_peaso_privesc_batch_existing_definition.py</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_athena_sessions.py, tests/test_peaso_privesc_batch_existing_definition.py</x:v>
+      </x:c>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K22" s="6" t="str"/>
+      <x:c r="L22" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M22" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N22" s="6" t="str">
+        <x:v>IDLE PySpark 3 session joined to exact GetSession execution role and containing workgroup; StartCalculationExecution grant on workgroup, wrong engine/state/workgroup and denied-detail negatives; tests/test_peaso_privesc_athena_sessions.py; AWS GetSession, SessionStatus and Spark API support.</x:v>
+      </x:c>
+      <x:c r="O22" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -845,10 +1233,27 @@
       </x:c>
       <x:c r="F23" s="6" t="str"/>
       <x:c r="G23" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="str"/>
+      <x:c r="L23" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M23" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N23" s="6" t="str">
+        <x:v>Current audit: an existing Automation document version must use a caller-supplied assumeRole parameter equal to the exact target role. The source must have PassRole to ssm.amazonaws.com and StartAutomationExecution on the exact document or automation-definition resource; a fresh reviewed execution must show a useful successful step under that role that the source cannot perform directly. The generic full-credential attestation was removed because the technique executes a runbook rather than handing the caller full role credentials. Scoped document and $LATEST definition grants, missing/wrong document or role, stale/duplicate proof, absent Start grant, wrong trust and directly permitted action have positive/negative regressions; historical catalog binding passes. AWS Automation setup, service authorization, StartAutomationExecution and Automation variables docs.</x:v>
+      </x:c>
+      <x:c r="O23" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -868,11 +1273,26 @@
       <x:c r="F24" s="6" t="str">
         <x:v>tests/test_peaso_privesc_facts_followups.py</x:v>
       </x:c>
-      <x:c r="G24" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G24" s="6" t="str"/>
       <x:c r="H24" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_facts_followups.py</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str"/>
+      <x:c r="J24" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="str"/>
+      <x:c r="L24" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M24" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N24" s="6" t="str">
+        <x:v>Exact target ECS-task-trusting role and PassRole, unused Batch job-definition name and revision, matching RegisterJobDefinition plus SubmitJob on both revision and enabled valid EC2 job queue, linked compute environment and complete inventories checked; queue-only, definition-only, disabled queue, Fargate and absent inventory negatives/unknown; tests/test_peaso_privesc_facts_followups.py; AWS Batch IAM resource-scoping guide, Service Authorization Reference, JobQueueDetail and ComputeEnvironmentDetail APIs</x:v>
+      </x:c>
+      <x:c r="O24" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -893,10 +1313,27 @@
         <x:v>tests/test_peaso_privesc_batch_existing_definition.py</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_batch_existing_definition.py</x:v>
       </x:c>
       <x:c r="H25" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_batch_existing_definition.py</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str"/>
+      <x:c r="J25" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="str"/>
+      <x:c r="L25" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M25" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N25" s="6" t="str">
+        <x:v>Exact ACTIVE container definition revision and projected jobRoleArn; usable EC2 queue and compute environment; SubmitJob checked on definition and queue ARNs; missing inventory unresolved, wrong role/revision/queue/state/platform and split-grant negatives; tests/test_peaso_privesc_batch_existing_definition.py; AWS SubmitJob and IAM restrict-job-submission docs.</x:v>
+      </x:c>
+      <x:c r="O25" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -917,10 +1354,27 @@
       </x:c>
       <x:c r="F26" s="6" t="str"/>
       <x:c r="G26" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H26" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I26" s="6" t="str"/>
+      <x:c r="J26" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K26" s="6" t="str"/>
+      <x:c r="L26" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M26" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N26" s="6" t="str">
+        <x:v>Current audit: UpdateFunctionCode must cover the exact active unqualified Lambda function whose current code hash and execution role are recorded. A fresh reviewed witness must bind an invocable ready Bedrock alias and routed version to an enabled action group using that same function, confirm Bedrock Lambda invoke permission, successful code update and InvokeAgent action-group invocation, and a useful action under the exact role unavailable directly to the caller. Published Lambda versions, wrong aliases/functions, stale or duplicate proofs and missing observed effects remain unresolved. Positive and negative regression and historical binding pass. AWS Bedrock action-group Lambda permissions, deployment, and Lambda version documentation.</x:v>
+      </x:c>
+      <x:c r="O26" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -941,10 +1395,27 @@
       </x:c>
       <x:c r="F27" s="6" t="str"/>
       <x:c r="G27" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H27" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I27" s="6" t="str"/>
+      <x:c r="J27" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="str"/>
+      <x:c r="L27" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M27" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N27" s="6" t="str">
+        <x:v>Current audit: AWS automatically creates DEFAULT with CreateAgentRuntime, so CreateAgentRuntimeEndpoint is no longer required. IAM PassRole, region, fresh generated name, InvokeAgentRuntime on runtime and DEFAULT endpoint, and service trust remain bound. A concrete role edge requires a fresh reviewed current READY runtime/version and DEFAULT endpoint using the exact role ID, controlled pullable artifact, successful invocation and useful role action unavailable directly to the caller. Missing, duplicate, stale, wrong-role, wrong-version and direct-caller evidence remains unresolved. Focused positive/negative and historical-binding tests pass. AWS AgentCore runtime versioning and invocation docs.</x:v>
+      </x:c>
+      <x:c r="O27" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -965,10 +1436,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_api_evidence_static_20261020.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H28" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_api_evidence_static_20261020.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I28" s="6" t="str"/>
+      <x:c r="J28" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K28" s="6" t="str"/>
+      <x:c r="L28" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M28" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N28" s="6" t="str">
+        <x:v>Current sign-off: CreateCodeInterpreter is a global-resource action; exact service PassRole, Region, service trust and both generated-ID Start/Invoke grants are checked. Broad-name grants use a deterministic fresh name; fixed-name grants require complete native Code Interpreter inventory and a free name. SourceArn-conditioned trust, missing inventory and unverified boundary/SCP conditions stay unknown. Positive, occupied-name, missing-inventory, disjoint-name, wrong-resource and trust regressions pass in tests/test_peaso_privesc_aws_followups.py. AWS CreateCodeInterpreter/GetCodeInterpreter and service authorization docs.</x:v>
+      </x:c>
+      <x:c r="O28" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -989,10 +1477,27 @@
       </x:c>
       <x:c r="F29" s="6" t="str"/>
       <x:c r="G29" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H29" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I29" s="6" t="str"/>
+      <x:c r="J29" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K29" s="6" t="str"/>
+      <x:c r="L29" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M29" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N29" s="6" t="str">
+        <x:v>Current audit: CreateHarness, CreateAgentRuntime and CreateMemory account-level grants, PassRole with AgentCore service context, GetMemory and InvokeHarness/InvokeAgentRuntime/InvokeAgentRuntimeCommand on one generated harness scope remain required. A concrete role edge now needs fresh reviewed evidence of a READY harness version using the exact role ID, managed image readiness, active session, successful command, and useful action under the role unavailable directly to the caller. Missing, duplicate, stale, wrong-role, failed-command and direct-caller evidence stays unresolved. Focused positive/negative and historical-binding tests pass. AWS AgentCore Harness security and GetHarness docs.</x:v>
+      </x:c>
+      <x:c r="O29" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1013,10 +1518,27 @@
       </x:c>
       <x:c r="F30" s="6" t="str"/>
       <x:c r="G30" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_api_evidence_static_20261020.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H30" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_api_evidence_static_20261020.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I30" s="6" t="str"/>
+      <x:c r="J30" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K30" s="6" t="str"/>
+      <x:c r="L30" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M30" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N30" s="6" t="str">
+        <x:v>Current audit: exact READY runtime and DEFAULT endpoint, UpdateAgentRuntime, both InvokeAgentRuntime resource grants, PassRole service and associated-resource context, and trust remain required. A concrete edge also requires fresh reviewed evidence of the current runtime version under the exact role ID, controlled pullable replacement artifact, DEFAULT serving that version, a new session, successful invocation and useful role action unavailable directly to the caller. Missing, duplicate, stale, wrong-version, wrong-role, old-session and direct-caller evidence stays unresolved. Focused positive/negative and historical-binding tests pass. AWS AgentCore versioning and update docs.</x:v>
+      </x:c>
+      <x:c r="O30" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1035,10 +1557,27 @@
       <x:c r="E31" s="6" t="str"/>
       <x:c r="F31" s="6" t="str"/>
       <x:c r="G31" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_braket_script.py</x:v>
       </x:c>
       <x:c r="H31" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_braket_script.py</x:v>
+      </x:c>
+      <x:c r="I31" s="6" t="str"/>
+      <x:c r="J31" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K31" s="6" t="str"/>
+      <x:c r="L31" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M31" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N31" s="6" t="str">
+        <x:v>AWS Braket CreateJob and SearchDevices APIs and Service Authorization Reference confirm required device and generated-job resource authorization, required exact deviceArn search filter, scriptModeConfig S3 archive and output S3 path. The evaluator now requires an observed ONLINE SV1 simulator in the Region, scoped CreateJob grants on that device and all generated job ARNs, exact Braket PassRole and service trust, source PutObject and target-role GetObject on the same script archive, and a target-role PutObject grant covering the output prefix in a same-Region bucket with complete policy/encryption facts. Other devices, images, missing inventories and complex S3 paths remain UNKNOWN; scheduling and execution remain conditional. Positive distinct-bucket and exact custom archive tests plus absent/offline/denied device, device-only/job-only, wrong Region, missing S3 rights, bucket deny/KMS, wrong trust/service negatives pass. Collector SearchDevices filter and customer-role permission verified; all managed policies remain under 6144 characters and historical binding is retained.</x:v>
+      </x:c>
+      <x:c r="O31" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1059,10 +1598,27 @@
         <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="G32" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="H32" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
+      </x:c>
+      <x:c r="I32" s="6" t="str"/>
+      <x:c r="J32" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K32" s="6" t="str"/>
+      <x:c r="L32" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M32" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N32" s="6" t="str">
+        <x:v>TagResource and PutCaseEventConfiguration both use the exact Cases domain ARN; pre-existing aws:ResourceTag/Access condition, accepted Access=Operator tag, all evaluated resources, prior denial and effective new permission checked; missing/duplicate/wrong-domain/nonwriter negatives; tests/test_peaso_privesc_aws_scoped_grants.py; AWS Connect Cases Service Authorization Reference and PutCaseEventConfiguration API</x:v>
+      </x:c>
+      <x:c r="O32" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1081,10 +1637,27 @@
       <x:c r="E33" s="6" t="str"/>
       <x:c r="F33" s="6" t="str"/>
       <x:c r="G33" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H33" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I33" s="6" t="str"/>
+      <x:c r="J33" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K33" s="6" t="str"/>
+      <x:c r="L33" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M33" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N33" s="6" t="str">
+        <x:v>Reviewed AWS Cloud Control CreateResource authorization, supported AWS::IAM::User resource, and IAM User LoginProfile/ManagedPolicyArns/Policies properties. The current precondition binds a CloudFormation-trusting passable role to CreateUser, GetUser, CreateLoginProfile and either AttachUserPolicy for AdministratorAccess or PutUserPolicy on one unused user ARN; same-account scope and quota are checked. Focused current-catalog test passes for managed and inline admin branches and rejects missing password/read, wrong trust, missing PassRole, non-admin policy and occupied exact user name. CreateResource now requires a global Resource grant in the precondition; a policy scoped to an existing stack ARN cannot make an administrator edge. AWS Cloud Control API Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O33" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1098,19 +1671,32 @@
         <x:v>checked</x:v>
       </x:c>
       <x:c r="D34" s="6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E34" s="6" t="str">
-        <x:v>cloudformation_attached_role_changeset_executable</x:v>
-      </x:c>
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="str"/>
       <x:c r="F34" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G34" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G34" s="6" t="str"/>
       <x:c r="H34" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I34" s="6" t="str"/>
+      <x:c r="J34" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K34" s="6" t="str"/>
+      <x:c r="L34" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M34" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N34" s="6" t="str">
+        <x:v>Existing updatable stack joined to its recorded service role; CreateChangeSet and ExecuteChangeSet both required on same stack; no PassRole; role and permission mismatch negatives; tests/test_peaso_privesc_schema_ext.py; AWS CreateChangeSet and ExecuteChangeSet APIs</x:v>
+      </x:c>
+      <x:c r="O34" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1131,10 +1717,27 @@
       </x:c>
       <x:c r="F35" s="6" t="str"/>
       <x:c r="G35" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H35" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I35" s="6" t="str"/>
+      <x:c r="J35" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K35" s="6" t="str"/>
+      <x:c r="L35" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M35" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N35" s="6" t="str">
+        <x:v>Current audit: IAM PassRole to cloudformation.amazonaws.com and the exact CreateStack, CreateChangeSet plus ExecuteChangeSet, or UpdateStack route remain required. A concrete role edge needs one fresh reviewed caller-controlled template effect using the exact role ID, operation, stack, action and resource, with a useful outcome unavailable directly to the caller. CREATE change sets must be executed; updates must bind the same recorded stack. Missing, stale, duplicate, wrong-role, wrong-operation, read-only and direct-caller cases remain unresolved. Focused positive and negative tests pass; AWS CloudFormation service-role and stack API documentation.</x:v>
+      </x:c>
+      <x:c r="O35" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1155,10 +1758,27 @@
       </x:c>
       <x:c r="F36" s="6" t="str"/>
       <x:c r="G36" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H36" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I36" s="6" t="str"/>
+      <x:c r="J36" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K36" s="6" t="str"/>
+      <x:c r="L36" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M36" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N36" s="6" t="str">
+        <x:v>Current audit: IAM PassRole to cloudformation.amazonaws.com and the exact CreateStack, CreateChangeSet plus ExecuteChangeSet, or UpdateStack route remain required. A concrete role edge needs one fresh reviewed caller-controlled template effect using the exact role ID, operation, stack, action and resource, with a useful outcome unavailable directly to the caller. CREATE change sets must be executed; updates must bind the same recorded stack. Missing, stale, duplicate, wrong-role, wrong-operation, read-only and direct-caller cases remain unresolved. Focused positive and negative tests pass; AWS CloudFormation service-role and stack API documentation.</x:v>
+      </x:c>
+      <x:c r="O36" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1179,10 +1799,27 @@
       </x:c>
       <x:c r="F37" s="6" t="str"/>
       <x:c r="G37" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_followups.py</x:v>
       </x:c>
       <x:c r="H37" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_followups.py</x:v>
+      </x:c>
+      <x:c r="I37" s="6" t="str"/>
+      <x:c r="J37" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K37" s="6" t="str"/>
+      <x:c r="L37" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M37" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N37" s="6" t="str">
+        <x:v>Current audit: PassRole to the administration role, its ability to assume the execution role, and CreateStackSet/CreateStackInstances or exact existing SELF_MANAGED UpdateStackSet permissions remain required. A concrete execution-role edge needs fresh reviewed evidence that the exact administration and execution role IDs were used for a successful caller-controlled deployment in the target account and Region, producing a useful role operation unavailable directly to the source. Missing, duplicate, stale, wrong-role, wrong-account, wrong-operation and direct-caller evidence stays unresolved. New and update positive/negative tests and historical binding pass. AWS self-managed StackSets role guidance.</x:v>
+      </x:c>
+      <x:c r="O37" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1203,10 +1840,27 @@
       </x:c>
       <x:c r="F38" s="6" t="str"/>
       <x:c r="G38" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H38" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I38" s="6" t="str"/>
+      <x:c r="J38" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K38" s="6" t="str"/>
+      <x:c r="L38" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M38" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N38" s="6" t="str">
+        <x:v>Current audit: IAM PassRole to cloudformation.amazonaws.com and the exact CreateStack, CreateChangeSet plus ExecuteChangeSet, or UpdateStack route remain required. A concrete role edge needs one fresh reviewed caller-controlled template effect using the exact role ID, operation, stack, action and resource, with a useful outcome unavailable directly to the caller. CREATE change sets must be executed; updates must bind the same recorded stack. Missing, stale, duplicate, wrong-role, wrong-operation, read-only and direct-caller cases remain unresolved. Focused positive and negative tests pass; AWS CloudFormation service-role and stack API documentation.</x:v>
+      </x:c>
+      <x:c r="O38" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1227,10 +1881,27 @@
       </x:c>
       <x:c r="F39" s="6" t="str"/>
       <x:c r="G39" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H39" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I39" s="6" t="str"/>
+      <x:c r="J39" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K39" s="6" t="str"/>
+      <x:c r="L39" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M39" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N39" s="6" t="str">
+        <x:v>Current audit: RegisterType, PassRole to resources.cloudformation.amazonaws.com, an owned S3 package readable and writable by the source, and a Cloud Control CreateResource or stack invocation route remain required. A concrete edge now also needs fresh reviewed evidence that this private resource handler registered and ran under the exact role ID, performed an action allowed by that role and unavailable directly to the caller, and produced a useful effect. Missing, stale, duplicate, wrong-role, wrong-package, failed-handler, read-only, and direct-caller cases stay unresolved. Focused positive, negative and historical-binding tests pass; AWS private extension and Cloud Control authorization documentation.</x:v>
+      </x:c>
+      <x:c r="O39" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1251,10 +1922,27 @@
       </x:c>
       <x:c r="F40" s="6" t="str"/>
       <x:c r="G40" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H40" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I40" s="6" t="str"/>
+      <x:c r="J40" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K40" s="6" t="str"/>
+      <x:c r="L40" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M40" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N40" s="6" t="str">
+        <x:v>Current audit: management-account source, enabled Organizations trusted access, member OU, CreateStackSet and CreateStackInstances permissions remain required. A concrete account-admin edge now needs fresh reviewed evidence of a successful SERVICE_MANAGED deployment into the exact member account and Region plus usable administrator credentials for an exact recorded IAM role or user. AssumeRole and access-key paths are both supported; missing, duplicate, stale, wrong-member, wrong-OU, disabled access, invalid credentials and absent principal inventory remain unresolved. Focused positive/negative tests and historical binding pass. AWS service-managed StackSets trusted-access guidance.</x:v>
+      </x:c>
+      <x:c r="O40" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1268,19 +1956,32 @@
         <x:v>checked</x:v>
       </x:c>
       <x:c r="D41" s="6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E41" s="6" t="str">
-        <x:v>cloudformation_attached_role_stack_updatable</x:v>
-      </x:c>
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E41" s="6" t="str"/>
       <x:c r="F41" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G41" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G41" s="6" t="str"/>
       <x:c r="H41" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I41" s="6" t="str"/>
+      <x:c r="J41" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K41" s="6" t="str"/>
+      <x:c r="L41" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M41" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N41" s="6" t="str">
+        <x:v>Existing updatable stack joined to its recorded service role; UpdateStack permission bound to same stack; AWS confirms attached role reused without PassRole; status and role mismatch negatives; tests/test_peaso_privesc_schema_ext.py; AWS UpdateStack API and service-role guide</x:v>
+      </x:c>
+      <x:c r="O41" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -1301,10 +2002,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G42" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H42" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I42" s="6" t="str"/>
+      <x:c r="J42" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K42" s="6" t="str"/>
+      <x:c r="L42" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M42" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N42" s="6" t="str">
+        <x:v>Exact Lambda@Edge role trust to lambda.amazonaws.com and edgelambda.amazonaws.com, iam:PassRole to Lambda, unused us-east-1 function, CreateFunction/PublishVersion on same function, GetFunction and Enable/DisableReplication on numbered version checked. The distribution branch accepts global CreateDistribution without existing distribution inventory or UpdateDistribution on an exact deployed distribution ARN. Missing distribution action, invalid resource-scoped CreateDistribution, missing SLR, missing replication action, disjoint function names and occupied name negatives pass; tests/test_peaso_privesc_aws_followups.py. Invocation remains conditional on deployment and traffic; AWS CloudFront Lambda@Edge permissions guide and CloudFront/Lambda Service Authorization References.</x:v>
+      </x:c>
+      <x:c r="O42" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -1325,10 +2043,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G43" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H43" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I43" s="6" t="str"/>
+      <x:c r="J43" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K43" s="6" t="str"/>
+      <x:c r="L43" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M43" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N43" s="6" t="str">
+        <x:v>CodeBuild role trust and PassRole, available valid project name, CreateProject and StartBuild on one project, controllable inline buildspec, and separate batch-role trust, PassRole, and child-build grant checked; disjoint names, occupied name, missing inventory, wrong role condition, and batch negatives; tests/test_peaso_privesc_aws_followups.py; AWS CreateProject, StartBuild, and StartBuildBatch APIs</x:v>
+      </x:c>
+      <x:c r="O43" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -1349,10 +2084,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G44" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H44" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I44" s="6" t="str"/>
+      <x:c r="J44" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K44" s="6" t="str"/>
+      <x:c r="L44" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M44" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N44" s="6" t="str">
+        <x:v>CodeBuild role trust and PassRole, recorded existing project bound to exact account and Region ARN, UpdateProject and StartBuild on same project, controllable buildspec, and batch-role child-build grant checked; absent project, disjoint permission, wrong role condition, wrong Region ARN, and batch negatives; tests/test_peaso_privesc_aws_followups.py; AWS UpdateProject, StartBuild, and StartBuildBatch APIs</x:v>
+      </x:c>
+      <x:c r="O44" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -1375,10 +2127,27 @@
         <x:v>tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
       </x:c>
       <x:c r="G45" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_v4_all_id_proofs.py, tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
       </x:c>
       <x:c r="H45" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_v4_all_id_proofs.py, tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
+      </x:c>
+      <x:c r="I45" s="6" t="str"/>
+      <x:c r="J45" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K45" s="6" t="str"/>
+      <x:c r="L45" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M45" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N45" s="6" t="str">
+        <x:v>BatchGetProjects and BatchGetBuilds both authorized on exact project ARN; build branch additionally binds observed build ARN to project, partition/account/Region; reviewed successful credential read/authentication and exact newly allowed action/resource required; missing, wrong-build, wrong-resource and conflicting negatives; tests/test_peaso_privesc_v4_exact_user_credentials.py and test_peaso_privesc_v4_all_id_proofs.py; AWS CodeBuild Service Authorization Reference and environment variable guide</x:v>
+      </x:c>
+      <x:c r="O45" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1399,10 +2168,27 @@
       </x:c>
       <x:c r="F46" s="6" t="str"/>
       <x:c r="G46" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H46" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I46" s="6" t="str"/>
+      <x:c r="J46" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K46" s="6" t="str"/>
+      <x:c r="L46" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M46" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N46" s="6" t="str">
+        <x:v>Current audit: exact IN_PROGRESS CodeBuild build ID/ARN and actual build service role must be joined to its BatchGetBuilds debug session target, enabled session and paused breakpoint. A fresh reviewed StartSession and shell command must perform a useful action with the build role that the source cannot perform directly; source StartSession authorization must cover the exact recorded target. The generic full-credential attestation was removed because the path is live build shell execution, not a credential transfer. Missing, stale, duplicate, other-build/role/target, unpaused, no-shell-effect and direct-caller cases stay unresolved or absent. Focused positive/negative tests and historical binding pass. AWS CodeBuild Session Manager guide, DebugSession API and SSM StartSession authorization reference.</x:v>
+      </x:c>
+      <x:c r="O46" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1423,10 +2209,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G47" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H47" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I47" s="6" t="str"/>
+      <x:c r="J47" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K47" s="6" t="str"/>
+      <x:c r="L47" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M47" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N47" s="6" t="str">
+        <x:v>Recorded project and exact service-role attachment, exact StartBuild buildspec override or batch child-build grant, current CodeBuild role trust, and project ARN binding checked; wrong trust, missing override permission, missing batch grant, and mismatched ARN negatives; tests/test_peaso_privesc_aws_followups.py; AWS StartBuild and StartBuildBatch APIs</x:v>
+      </x:c>
+      <x:c r="O47" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1447,10 +2250,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G48" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H48" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I48" s="6" t="str"/>
+      <x:c r="J48" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K48" s="6" t="str"/>
+      <x:c r="L48" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M48" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N48" s="6" t="str">
+        <x:v>Exact recorded RUN_SANDBOX ARN and service role, StartCommandExecution permission, stopped and wrong-role negatives, and missing inventory unknown checked; tests/test_peaso_privesc_aws_followups.py; AWS StartCommandExecution API</x:v>
+      </x:c>
+      <x:c r="O48" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1471,10 +2291,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G49" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H49" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I49" s="6" t="str"/>
+      <x:c r="J49" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K49" s="6" t="str"/>
+      <x:c r="L49" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M49" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N49" s="6" t="str">
+        <x:v>Recorded project role, current CodeBuild trust, StartSandbox on project and command or connection permission on future sandbox ARN checked; wrong trust, wrong sandbox scope, and missing start negatives; tests/test_peaso_privesc_aws_followups.py; AWS StartSandbox, StartCommandExecution, and StartSandboxConnection APIs</x:v>
+      </x:c>
+      <x:c r="O49" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1495,10 +2332,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G50" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H50" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I50" s="6" t="str"/>
+      <x:c r="J50" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K50" s="6" t="str"/>
+      <x:c r="L50" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M50" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N50" s="6" t="str">
+        <x:v>Exact recorded RUN_SANDBOX ARN and service role, StartSandboxConnection permission, stopped and wrong-role negatives, and missing inventory unknown checked; Session Manager agent remains conditional; tests/test_peaso_privesc_aws_followups.py; AWS StartSandboxConnection API</x:v>
+      </x:c>
+      <x:c r="O50" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1519,10 +2373,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G51" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H51" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I51" s="6" t="str"/>
+      <x:c r="J51" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K51" s="6" t="str"/>
+      <x:c r="L51" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M51" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N51" s="6" t="str">
+        <x:v>Recorded project and exact service-role attachment, UpdateProject buildspec change, matching StartBuild permission or batch child-build grant, current CodeBuild trust, and project ARN binding checked; wrong trust, missing change/start permission, batch grant, and mismatched ARN negatives; tests/test_peaso_privesc_aws_followups.py; AWS UpdateProject, StartBuild, and StartBuildBatch APIs</x:v>
+      </x:c>
+      <x:c r="O51" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1543,10 +2414,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G52" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H52" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I52" s="6" t="str"/>
+      <x:c r="J52" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K52" s="6" t="str"/>
+      <x:c r="L52" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M52" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N52" s="6" t="str">
+        <x:v>Exact PassRole grants for CodeBuild and CodePipeline roles, same project and pipeline create/start grants, enabled S3 source versioning, source ZIP write, and artifact permissions checked; disjoint resource and missing permission negatives; tests/test_peaso_privesc_aws_followups.py; AWS S3 source and CodeBuild action references</x:v>
+      </x:c>
+      <x:c r="O52" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -1567,10 +2455,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G53" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H53" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I53" s="6" t="str"/>
+      <x:c r="J53" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K53" s="6" t="str"/>
+      <x:c r="L53" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M53" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N53" s="6" t="str">
+        <x:v>Same-account CodeBuild and CodePipeline roles, exact PassRole and create/start grants, usable CodeCommit branch or GitPush, repository archive permissions, and artifact access checked; missing optional branch evidence now stays unknown; tests/test_peaso_privesc_aws_followups.py; AWS CodeCommit and CodeBuild action references</x:v>
+      </x:c>
+      <x:c r="O53" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -1591,10 +2496,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G54" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H54" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I54" s="6" t="str"/>
+      <x:c r="J54" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K54" s="6" t="str"/>
+      <x:c r="L54" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M54" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N54" s="6" t="str">
+        <x:v>Same-account roles, exact PassRole and create/start grants, tagged ECR image and DescribeImages permission, and build artifact access checked; missing image inventory stays unknown; tests/test_peaso_privesc_aws_followups.py; AWS ECR and CodeBuild action references</x:v>
+      </x:c>
+      <x:c r="O54" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -1615,10 +2537,27 @@
       </x:c>
       <x:c r="F55" s="6" t="str"/>
       <x:c r="G55" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H55" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I55" s="6" t="str"/>
+      <x:c r="J55" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K55" s="6" t="str"/>
+      <x:c r="L55" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M55" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N55" s="6" t="str">
+        <x:v>Current audit: source StartPipelineExecution, pipeline/action role trust and exact StartBuild, existing CODEPIPELINE project role or authorized override, UpdateProject buildspec and batch requirements still join to one configured pipeline action. A configured input artifact name alone never proves delivery. A concrete role effect now requires a fresh reviewed execution bound to hashes of the exact pipeline and project definitions, matching produced and consumed input artifacts, changed buildspec used by the build, and a useful role action unavailable directly to the source. Earlier non-Source actions can also produce inputs. Missing, disjoint, stale, duplicate and malformed witness cases remain unresolved; focused positive/negative tests and historical binding pass. AWS CodePipeline CodeBuild action, action declaration and artifact documentation.</x:v>
+      </x:c>
+      <x:c r="O55" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1637,10 +2576,27 @@
       <x:c r="E56" s="6" t="str"/>
       <x:c r="F56" s="6" t="str"/>
       <x:c r="G56" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
       </x:c>
       <x:c r="H56" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
+      </x:c>
+      <x:c r="I56" s="6" t="str"/>
+      <x:c r="J56" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K56" s="6" t="str"/>
+      <x:c r="L56" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M56" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N56" s="6" t="str">
+        <x:v>Exact pool-scoped GetOpenIdTokenForDeveloperIdentity permission and collected DeveloperProviderName plus Roles.authenticated are joined to the same pool; target trust must admit cognito-identity.amazonaws.com with matching aud and authenticated amr. Guest and mapped roles are excluded. Focused tests cover evaluator reach, wrong pool, absent provider/role, incompatible trust, explicit deny, unresolved NotPrincipal deny and incomplete collection; AWS Cognito API and IAM trust docs.</x:v>
+      </x:c>
+      <x:c r="O56" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -1659,10 +2615,27 @@
       <x:c r="E57" s="6" t="str"/>
       <x:c r="F57" s="6" t="str"/>
       <x:c r="G57" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
       </x:c>
       <x:c r="H57" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
+      </x:c>
+      <x:c r="I57" s="6" t="str"/>
+      <x:c r="J57" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K57" s="6" t="str"/>
+      <x:c r="L57" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M57" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N57" s="6" t="str">
+        <x:v>AWS developer-authenticated identity and Basic authentication docs confirm a developer token can be exchanged through STS for a chosen role. The selector requires a collected pool with DeveloperProviderName and AllowClassicFlow=true, exact GetOpenIdTokenForDeveloperIdentity permission on that same pool, and matching role web-identity trust. Cross-account roles need explicit aud and amr conditions. Focused tests cover nondefault and cross-account roles plus disabled flow and wrong-pool permission; predecessor catalog retained exactly.</x:v>
+      </x:c>
+      <x:c r="O57" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -1681,10 +2654,27 @@
       <x:c r="E58" s="6" t="str"/>
       <x:c r="F58" s="6" t="str"/>
       <x:c r="G58" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
       </x:c>
       <x:c r="H58" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
+      </x:c>
+      <x:c r="I58" s="6" t="str"/>
+      <x:c r="J58" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K58" s="6" t="str"/>
+      <x:c r="L58" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M58" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N58" s="6" t="str">
+        <x:v>The subset with a developer provider is exact: SetIdentityPoolRoles (resource=*), iam:PassRole on the target, and GetOpenIdTokenForDeveloperIdentity on the same collected pool. The target is a same-account IAM role whose trust admits the pool audience and authenticated developer method. Tests cover the positive route, each missing action, wrong pool, wrong PassRole service, absent provider and wrong trust. AWS SetIdentityPoolRoles, Cognito role-based access and developer-authenticated identity docs.</x:v>
+      </x:c>
+      <x:c r="O58" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -1703,10 +2693,27 @@
       <x:c r="E59" s="6" t="str"/>
       <x:c r="F59" s="6" t="str"/>
       <x:c r="G59" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
       </x:c>
       <x:c r="H59" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_developer.py</x:v>
+      </x:c>
+      <x:c r="I59" s="6" t="str"/>
+      <x:c r="J59" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K59" s="6" t="str"/>
+      <x:c r="L59" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M59" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N59" s="6" t="str">
+        <x:v>The developer-token subset requires a collected pool with DeveloperProviderName, complete required UpdateIdentityPool fields and Basic flow currently disabled. The source must hold UpdateIdentityPool and GetOpenIdTokenForDeveloperIdentity on that same pool. A target role must trust the pool and authenticated developer method; cross-account roles need explicit aud/amr. Focused tests cover enabled/disabled flow, missing action, wrong pool, missing configuration, absent provider and cross-account role. AWS UpdateIdentityPool, developer-authenticated identities and Cognito IAM role docs.</x:v>
+      </x:c>
+      <x:c r="O59" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -1725,10 +2732,27 @@
       <x:c r="E60" s="6" t="str"/>
       <x:c r="F60" s="6" t="str"/>
       <x:c r="G60" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_guest_classic_update.py</x:v>
       </x:c>
       <x:c r="H60" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_cognito_guest_classic_update.py</x:v>
+      </x:c>
+      <x:c r="I60" s="6" t="str"/>
+      <x:c r="J60" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K60" s="6" t="str"/>
+      <x:c r="L60" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M60" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N60" s="6" t="str">
+        <x:v>UpdateIdentityPool on an exact collected pool can enable both guest access and Basic flow. A public guest token can then be exchanged for a role whose web-identity trust admits that pool audience and unauthenticated method, including a cross-account role with explicit aud/amr trust. The selector requires a usable pool name, complete empty RoleMappings, at least one currently disabled flow flag, same-account update permission and exact target trust. Focused tests cover the positive route, cross-account role, wrong pool/action/trust, role mappings, missing pool details and explicit trust deny. AWS UpdateIdentityPool, Cognito authentication-flow and IAM roles docs.</x:v>
+      </x:c>
+      <x:c r="O60" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -1749,10 +2773,27 @@
       </x:c>
       <x:c r="F61" s="6" t="str"/>
       <x:c r="G61" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H61" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I61" s="6" t="str"/>
+      <x:c r="J61" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K61" s="6" t="str"/>
+      <x:c r="L61" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M61" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N61" s="6" t="str">
+        <x:v>Current audit: exact PassRole to ssm.amazonaws.com remains required. PutRemediationConfigurations is checked on the exact configuration ARN from fresh reviewed evidence; ssm:CreateDocument is required only when the source created the document, so an existing document is a valid route. The witness must bind an existing non-service-linked rule, recording Config recorder, noncompliant compliance snapshot, automatic mode, ready remediation service-linked role, AutomationAssumeRole parameter equal to the passed role, actual remediation/Automation execution and useful role action unavailable directly to the source. Missing, wrong-service, wrong-rule/document/role, manual, stale, duplicate, disjoint Put grant and direct-caller cases remain unresolved or absent. Existing/new-document regressions and historical binding pass. AWS Config PutRemediationConfigurations API, setup guide and service authorization reference.</x:v>
+      </x:c>
+      <x:c r="O61" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1773,10 +2814,27 @@
       </x:c>
       <x:c r="F62" s="6" t="str"/>
       <x:c r="G62" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H62" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I62" s="6" t="str"/>
+      <x:c r="J62" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K62" s="6" t="str"/>
+      <x:c r="L62" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M62" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N62" s="6" t="str">
+        <x:v>Current audit: AWS Data Pipeline remains available only to existing customers (AWS documents July 2025 closure to new customers). CreatePipeline requires global resource authorization; PutPipelineDefinition and ActivatePipeline are checked on the exact generated pipeline ARN. Resource role PassRole is evaluated with iam:PassedToService=ec2.amazonaws.com and a separate pipeline role must be passable to datapipeline.amazonaws.com and trust that service. A fresh reviewed witness must bind both exact role IDs, EC2 instance profile, controlled ShellCommandActivity, activated pipeline, launched instance and useful role action unavailable directly to the source. Missing, wrong role/profile/pipeline, stale, duplicate, no customer eligibility, no shell effect and disjoint permissions remain unresolved or absent. Positive/negative tests and historical binding pass. AWS Data Pipeline IAM roles, ShellCommandActivity, service authorization and document history.</x:v>
+      </x:c>
+      <x:c r="O62" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -1797,10 +2855,27 @@
         <x:v>tests/test_peaso_aws_deadline_queue_inventory.py, tests/test_peaso_privesc_deadline_queue_vend.py</x:v>
       </x:c>
       <x:c r="G63" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_queue_vend.py</x:v>
       </x:c>
       <x:c r="H63" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_aws_deadline_queue_inventory.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_queue_vend.py</x:v>
+      </x:c>
+      <x:c r="I63" s="6" t="str"/>
+      <x:c r="J63" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K63" s="6" t="str"/>
+      <x:c r="L63" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M63" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N63" s="6" t="str">
+        <x:v>Collects exact queue-to-role bindings through ListFarms, ListQueues and GetQueue. Joins one same-account role with a derived AssumeQueueRoleForUser grant on the exact queue ARN and trust for the exact farm. Wrong queue scope, wrong attached role, wrong farm trust, missing inventory and unresolved membership condition negatives pass; tests/test_peaso_privesc_deadline_queue_vend.py and tests/test_peaso_aws_deadline_queue_inventory.py. Credential vending remains conditional on the live service request.</x:v>
+      </x:c>
+      <x:c r="O63" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -1819,10 +2894,27 @@
       <x:c r="E64" s="6" t="str"/>
       <x:c r="F64" s="6" t="str"/>
       <x:c r="G64" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_worker_vend.py</x:v>
       </x:c>
       <x:c r="H64" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_worker_vend.py</x:v>
+      </x:c>
+      <x:c r="I64" s="6" t="str"/>
+      <x:c r="J64" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K64" s="6" t="str"/>
+      <x:c r="L64" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M64" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N64" s="6" t="str">
+        <x:v>ListFarms, ListFleets, GetFleet and ListWorkers bind one existing worker to its exact fleet role. The evaluator checks a derived AssumeFleetRoleForWorker grant on that worker ARN and the role service trust for the same farm. Wrong worker scope, role, farm trust, stopped worker, missing inventory and unresolved membership conditions do not create a concrete edge. Focused inventory, policy and graph tests pass. AWS service-role guidance limits impact to worker permissions, not unrelated attached policies; credential vending remains conditional on the live API request.</x:v>
+      </x:c>
+      <x:c r="O64" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -1841,10 +2933,27 @@
       <x:c r="E65" s="6" t="str"/>
       <x:c r="F65" s="6" t="str"/>
       <x:c r="G65" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_worker_vend.py</x:v>
       </x:c>
       <x:c r="H65" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_worker_vend.py</x:v>
+      </x:c>
+      <x:c r="I65" s="6" t="str"/>
+      <x:c r="J65" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K65" s="6" t="str"/>
+      <x:c r="L65" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M65" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N65" s="6" t="str">
+        <x:v>ListFarms, ListFleets and GetFleet bind one active customer-managed fleet with room for a new worker to its exact role. The evaluator checks farm-scoped service trust, ListTagsForResource on that fleet and broad CreateWorker, AssumeFleetRoleForWorker and TagResource grants covering every generated worker ID on the fleet. Exact existing-worker grants, wrong fleet, full fleet, wrong mode, wrong trust and missing dependent permissions do not create a concrete edge. Focused inventory, graph, managed-policy-condition and current/prior binding tests pass. Live credential vending remains conditional.</x:v>
+      </x:c>
+      <x:c r="O65" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -1863,10 +2972,27 @@
       <x:c r="E66" s="6" t="str"/>
       <x:c r="F66" s="6" t="str"/>
       <x:c r="G66" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_deadline_passrole_queue.py</x:v>
       </x:c>
       <x:c r="H66" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_deadline_passrole_queue.py</x:v>
+      </x:c>
+      <x:c r="I66" s="6" t="str"/>
+      <x:c r="J66" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K66" s="6" t="str"/>
+      <x:c r="L66" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M66" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N66" s="6" t="str">
+        <x:v>Current audit: AWS Deadline Cloud service authorization confirms UpdateQueue and AssumeQueueRoleForUser are queue-scoped and queue creation has a generated queue ID. The evaluator now joins one collected existing queue and farm to the exact UpdateQueue and AssumeQueueRoleForUser grants, target role farm-scoped service trust, and iam:PassRole with iam:PassedToService=deadline.amazonaws.com. A queue already using the target role is handled by the separate existing-queue route. CreateQueue without a recorded generated queue remains UNKNOWN, so scoped grants are not missed as a negative or promoted to an unrelated role edge; a later recorded queue can use the existing-queue route. Positive, disjoint queue grants, wrong service/trust, unresolved membership, duplicate existing-role and missing/new-queue tests pass; current and predecessor catalog bindings verified. AWS Deadline Cloud service authorization reference, UpdateQueue, CreateQueue and queue-role documentation.</x:v>
+      </x:c>
+      <x:c r="O66" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -1887,10 +3013,27 @@
       </x:c>
       <x:c r="F67" s="6" t="str"/>
       <x:c r="G67" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_passrole_fleet_worker.py</x:v>
       </x:c>
       <x:c r="H67" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_deadline_passrole_fleet_worker.py</x:v>
+      </x:c>
+      <x:c r="I67" s="6" t="str"/>
+      <x:c r="J67" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K67" s="6" t="str"/>
+      <x:c r="L67" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M67" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N67" s="6" t="str">
+        <x:v>Current audit: AWS Deadline Cloud service-role documentation says extra fleet-role permissions do not take effect, so this technique now targets one verified Deadline worker operation rather than the whole IAM role. A fresh reviewed record must bind exact farm, fleet, worker, target role ID, successful CreateFleet or UpdateFleet, CreateWorker, AssumeFleetRoleForWorker and use of the resulting credentials for UpdateWorker, UpdateWorkerSchedule or BatchGetJobEntity previously unavailable to the source. Evaluator checks exact resource-scoped grants, dependent ListTagsForResource and conditional TagResource, PassRole with iam:PassedToService=deadline.amazonaws.com, farm-scoped target trust and action under the role; missing, stale, conflicting, wrong worker/role/action, disjoint grants and already allowed caller action do not produce a concrete edge. Create and update positive/negative tests and current/prior catalog binding pass. AWS Deadline Cloud service authorization reference and service-role/worker-host documentation.</x:v>
+      </x:c>
+      <x:c r="O67" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -1909,10 +3052,27 @@
       <x:c r="E68" s="6" t="str"/>
       <x:c r="F68" s="6" t="str"/>
       <x:c r="G68" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_devicefarm_route.py</x:v>
       </x:c>
       <x:c r="H68" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_devicefarm_route.py</x:v>
+      </x:c>
+      <x:c r="I68" s="6" t="str"/>
+      <x:c r="J68" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K68" s="6" t="str"/>
+      <x:c r="L68" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M68" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N68" s="6" t="str">
+        <x:v>Current route uses an existing project, an exact project-listed pool with at least one APPIUM_WEB_NODE compatible device, CreateUpload on that project, ScheduleRun on the project and pool plus all generated package/spec upload ARNs, and exact iam:PassRole to a role trusting devicefarm.amazonaws.com. The collector retains project/pool association from ListDevicePools; AWS pool ARNs are independent of project and may be accountless for curated pools. Positive and wrong-project, wrong-pool, single-upload, no-device, wrong-service/trust, and missing-inventory direct tests pass. Older catalog binding remains exact via retained 690-entry archive. Existing-test-spec and UpdateUpload variants remain separate candidates.</x:v>
+      </x:c>
+      <x:c r="O68" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -1933,10 +3093,27 @@
       </x:c>
       <x:c r="F69" s="6" t="str"/>
       <x:c r="G69" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_devicefarm_existing_spec.py, tests/test_peaso_privesc_exact_principal_tranche.py</x:v>
       </x:c>
       <x:c r="H69" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_devicefarm_existing_spec.py, tests/test_peaso_privesc_exact_principal_tranche.py</x:v>
+      </x:c>
+      <x:c r="I69" s="6" t="str"/>
+      <x:c r="J69" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K69" s="6" t="str"/>
+      <x:c r="L69" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M69" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N69" s="6" t="str">
+        <x:v>Current audit: AWS Device Farm ScheduleRun authorizes exact project, device pool and upload resources, and iam:PassRole uses iam:PassedToService=devicefarm.amazonaws.com. The route no longer requires Resource=* or CreateUpload. A full-principal attestation and fresh reviewed run evidence must bind one existing project, compatible pool, successful Appium Web Node test spec and package uploads in that project, controlled spec execution, exact passed role ID, and a useful role action unavailable directly to the source. The evaluator checks ScheduleRun on every referenced ARN and exact PassRole, and rejects wrong/cross-project uploads, incompatible pools, disjoint grants, wrong service, duplicate inventory, failed or unexecuted specs, stale or restricted credentials and wrong authority fingerprint. Positive, accountless pool, negative, principal evidence and current/prior binding tests pass. AWS ScheduleRun API, Device Farm service authorization reference and Upload API.</x:v>
+      </x:c>
+      <x:c r="O69" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -1956,11 +3133,26 @@
       <x:c r="F70" s="6" t="str">
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
-      <x:c r="G70" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G70" s="6" t="str"/>
       <x:c r="H70" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I70" s="6" t="str"/>
+      <x:c r="J70" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K70" s="6" t="str"/>
+      <x:c r="L70" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M70" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N70" s="6" t="str">
+        <x:v>Exact active same-account table and IAM user are joined by ARN. Effective PutResourcePolicy is required, prior GetItem and surviving identity or boundary denies block the route; a replaceable table-policy Deny does not. A direct user grant bypasses a boundary implicit deny; account-root delegation alone is not prior access. Only default AWS-owned encryption qualifies until KMS authorization can be joined. The target is one newly obtainable GetItem permission, not observed data access. Focused positive and rejection tests pass in tests/test_peaso_privesc_aws_followups.py; AWS DynamoDB resource-policy and encryption docs.</x:v>
+      </x:c>
+      <x:c r="O70" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -1981,10 +3173,27 @@
       </x:c>
       <x:c r="F71" s="6" t="str"/>
       <x:c r="G71" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_autoscaling_created_input.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H71" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_autoscaling_created_input.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I71" s="6" t="str"/>
+      <x:c r="J71" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K71" s="6" t="str"/>
+      <x:c r="L71" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M71" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N71" s="6" t="str">
+        <x:v>Current audit: AWS Auto Scaling validates EC2 RunInstances and iam:PassRole when a launch template is selected; CreateLaunchConfiguration is unavailable to accounts created on or after October 1, 2024, so that branch needs an accepted creation witness. The evaluator checks the exact created launch configuration or template ARN, CreateAutoScalingGroup or UpdateAutoScalingGroup on the exact group ARN, PassRole to ec2.amazonaws.com, and for a template every recorded RunInstances authorization resource. A fresh reviewed record must tie the group to the created launch input, a launched member instance, its applied profile and immutable role ID, executed controlled user data, and a useful role action unavailable directly to the source. Wrong input/group/profile/role, disjoint permissions, duplicate or stale evidence, unexecuted code and incomplete template resources do not create an edge. Create/update configuration and template positive/negative tests plus current/prior binding pass. AWS Auto Scaling launch-template permissions, launch-configuration availability and service authorization reference.</x:v>
+      </x:c>
+      <x:c r="O71" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -2005,10 +3214,27 @@
       </x:c>
       <x:c r="F72" s="6" t="str"/>
       <x:c r="G72" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H72" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I72" s="6" t="str"/>
+      <x:c r="J72" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K72" s="6" t="str"/>
+      <x:c r="L72" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M72" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N72" s="6" t="str">
+        <x:v>Same running Linux instance, current profile and role IDs, applied IMDS, exact ec2:osuser permission, accepted pushed key, SSH session using that key, and usable target-role credentials require one fresh reviewed witness; no witness remains UNKNOWN. Positive and wrong-host, wrong-user, stale, conflicting and missing-proof cases in test_peaso_privesc_aws_followups.py. Ordinary read-only collection cannot produce the runtime witness.</x:v>
+      </x:c>
+      <x:c r="O72" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -2027,10 +3253,27 @@
       <x:c r="E73" s="6" t="str"/>
       <x:c r="F73" s="6" t="str"/>
       <x:c r="G73" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H73" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I73" s="6" t="str"/>
+      <x:c r="J73" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K73" s="6" t="str"/>
+      <x:c r="L73" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M73" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N73" s="6" t="str">
+        <x:v>Reviewed against AWS launch-template and Auto Scaling permissions documentation. Evaluator now joins collected ASG direct/mixed override references to exact launch-template ARNs; $Latest needs CreateLaunchTemplateVersion, $Default also needs ModifyLaunchTemplate on the same ARN. Pinned versions and zero-capacity groups are excluded; incomplete inventory remains unresolved. Positive, negative, explicit deny, mixed override, and missing-inventory regressions pass. Later launch and user-data execution remain conditional.</x:v>
+      </x:c>
+      <x:c r="O73" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -2051,10 +3294,27 @@
       </x:c>
       <x:c r="F74" s="6" t="str"/>
       <x:c r="G74" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H74" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I74" s="6" t="str"/>
+      <x:c r="J74" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K74" s="6" t="str"/>
+      <x:c r="L74" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M74" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N74" s="6" t="str">
+        <x:v>Reviewed AWS EC2 user-data restart and ModifyInstanceAttribute authorization docs. IAM grants alone no longer emit a principal edge: a fresh exact reviewed fact must establish changed-user-data execution, role credentials, instance/profile/role identity and stop protection. Source permission is checked on userData attribute and the same instance; stopped instances need Modify+Start, running also need Stop and either disabled stop protection or permission to disable it. EBS root and enabled applied IMDS are required. Current-catalog focused tests cover verified, missing/stale/wrong proof, attribute-scoped grants, stopped branch, stop protection and invalid root device; missing proof is unresolved.</x:v>
+      </x:c>
+      <x:c r="O74" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -2075,10 +3335,27 @@
       </x:c>
       <x:c r="F75" s="6" t="str"/>
       <x:c r="G75" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_v4_batch.py</x:v>
       </x:c>
       <x:c r="H75" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_v4_batch.py</x:v>
+      </x:c>
+      <x:c r="I75" s="6" t="str"/>
+      <x:c r="J75" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K75" s="6" t="str"/>
+      <x:c r="L75" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M75" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N75" s="6" t="str">
+        <x:v>AWS Attach an IAM role to an instance and PassRole documentation reviewed. Exact native association/profile membership, PassRole context, reviewed instance control and IMDS proof already bound in ec2_profile_association.py. Fixed false positive: direct replacement requires running state; stopped state can use detach then associate plus StartInstances. Synthetic current-catalog evaluation verified stopped replacement absent, running replacement present, and stopped detach-associate present. SDK test expectation updated; full pytest collection remains blocked by unrelated AWS command reviewed_delta import failure.</x:v>
+      </x:c>
+      <x:c r="O75" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -2099,10 +3376,27 @@
       </x:c>
       <x:c r="F76" s="6" t="str"/>
       <x:c r="G76" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_spot_fleet_role_effect.py</x:v>
       </x:c>
       <x:c r="H76" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_spot_fleet_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I76" s="6" t="str"/>
+      <x:c r="J76" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K76" s="6" t="str"/>
+      <x:c r="L76" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M76" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N76" s="6" t="str">
+        <x:v>Current audit: AWS Spot Fleet uses a separate fleet service role and an EC2 instance-profile role, and RequestSpotFleet and RunInstances can require authorization on image, subnet, security group, fleet request, instance and other selected resources. The evaluator now requires fresh reviewed evidence of an accepted Spot Fleet request, immutable IDs and trust for both roles, complete exact authorization-resource lists, instance ownership by that fleet, applied profile, controlled user-data execution and a useful action under the instance role unavailable directly to the source. It checks PassRole for each role with its own service context and all listed RequestSpotFleet, RunInstances and requested tagging resources; missing, stale, duplicate or mismatched evidence does not create a concrete edge. Both documented fleet-role service contexts and tagging positive/negative tests plus historical binding pass. AWS Spot Fleet permissions and EC2 service authorization reference.</x:v>
+      </x:c>
+      <x:c r="O76" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -2123,10 +3417,29 @@
       </x:c>
       <x:c r="F77" s="6" t="str"/>
       <x:c r="G77" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc.py, tests/test_peaso_privesc_audit_fixes.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_integration.py, tests/test_peaso_privesc_runinstances_role_effect.py</x:v>
       </x:c>
       <x:c r="H77" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc.py, tests/test_peaso_privesc_audit_fixes.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_integration.py, tests/test_peaso_privesc_runinstances_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I77" s="6" t="str"/>
+      <x:c r="J77" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K77" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_runinstances_role_effect.py</x:v>
+      </x:c>
+      <x:c r="L77" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M77" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N77" s="6" t="str">
+        <x:v>Current audit: AWS RunInstances requires permissions over every selected launch resource, and iam:AssociatedResourceArn can scope PassRole to the new instance. The route now joins one fresh reviewed successful launch, exact image, instance, subnet, security group and network-interface authorization resources, an applied profile carrying the immutable target role ID, controlled user data execution using that role, and a useful role action unavailable to the source. PassRole is evaluated for the exact instance and service, plus requested tags. Absent, stale, duplicate or mismatched proof stays unresolved; disjoint permissions do not create a concrete edge. Focused positive, rejection, unresolved and historical-binding tests pass. AWS EC2 Service Authorization Reference, IAM condition-key reference and EC2 launch-policy examples.</x:v>
+      </x:c>
+      <x:c r="O77" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -2147,10 +3460,27 @@
       </x:c>
       <x:c r="F78" s="6" t="str"/>
       <x:c r="G78" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_spot_request_role_effect.py</x:v>
       </x:c>
       <x:c r="H78" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_spot_request_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I78" s="6" t="str"/>
+      <x:c r="J78" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K78" s="6" t="str"/>
+      <x:c r="L78" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M78" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N78" s="6" t="str">
+        <x:v>Current audit: AWS RequestSpotInstances authorizes the image, generated Spot request and selected network resources, with PassRole to EC2. The evaluator now requires one fresh reviewed accepted request fulfilled by the exact instance, service-linked-role readiness, complete request authorization resources, an applied profile carrying the immutable target role ID, executed controlled user data and a useful role action unavailable directly to the source. PassRole includes iam:AssociatedResourceArn for that instance, and requested tagging is checked. Missing, stale, duplicate or mismatched evidence stays unresolved; disjoint permissions do not create a concrete edge. Positive, negative, unresolved, prior-binding and current-binding tests pass. AWS EC2 Service Authorization Reference, Spot request and IAM condition-key documentation.</x:v>
+      </x:c>
+      <x:c r="O78" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -2169,10 +3499,27 @@
       <x:c r="E79" s="6" t="str"/>
       <x:c r="F79" s="6" t="str"/>
       <x:c r="G79" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H79" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I79" s="6" t="str"/>
+      <x:c r="J79" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K79" s="6" t="str"/>
+      <x:c r="L79" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M79" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N79" s="6" t="str">
+        <x:v>Reviewed the HackTricks ECScape route, ECS DescribeTasks/DescribeTaskDefinition fields and AWS task-execution-role guidance. The CSPM now uses exact container-instance placement and actual task or execution role ARNs, including task-level overrides; focused tests prove both co-located roles, reject another host, and preserve old catalog bindings. Agent impersonation still requires the source to hold the specific host instance-role session and reach its ACS channel; these runtime facts are not collected, so the catalog stays conditional and does not claim observed credential theft.</x:v>
+      </x:c>
+      <x:c r="O79" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -2193,10 +3540,27 @@
         <x:v>tests/test_peaso_privesc_ecs_exec_collector_projection.py, tests/test_peaso_privesc_ecs_exec_role.py</x:v>
       </x:c>
       <x:c r="G80" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_ecs_exec_role.py</x:v>
       </x:c>
       <x:c r="H80" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_ecs_exec_collector_projection.py, tests/test_peaso_privesc_ecs_exec_role.py</x:v>
+      </x:c>
+      <x:c r="I80" s="6" t="str"/>
+      <x:c r="J80" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K80" s="6" t="str"/>
+      <x:c r="L80" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M80" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N80" s="6" t="str">
+        <x:v>Exact running task, enabled Exec, running ExecuteCommandAgent, matching task role, ecs:ExecuteCommand on cluster and task, task-role ssmmessages permissions, configured Exec KMS grants and non-read-only root container are joined. Negative cases cover stopped tasks, missing agent, wrong task, missing channel or KMS permission and read-only root. Execution remains conditional on the task and agent staying live. tests/test_peaso_privesc_ecs_exec_role.py and tests/test_peaso_privesc_ecs_exec_collector_projection.py: 12 focused tests pass; AWS ECS Exec and service authorization docs.</x:v>
+      </x:c>
+      <x:c r="O80" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -2215,10 +3579,27 @@
       <x:c r="E81" s="6" t="str"/>
       <x:c r="F81" s="6" t="str"/>
       <x:c r="G81" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H81" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I81" s="6" t="str"/>
+      <x:c r="J81" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K81" s="6" t="str"/>
+      <x:c r="L81" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M81" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N81" s="6" t="str">
+        <x:v>Verified scoped RegisterTaskDefinition and RunTask over every new family revision, PassRole service context, same-Region active cluster with connected container instance; positive and missing, denied, wrong-cluster, disconnected-host cases in test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="O81" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -2237,10 +3618,27 @@
       <x:c r="E82" s="6" t="str"/>
       <x:c r="F82" s="6" t="str"/>
       <x:c r="G82" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H82" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I82" s="6" t="str"/>
+      <x:c r="J82" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K82" s="6" t="str"/>
+      <x:c r="L82" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M82" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N82" s="6" t="str">
+        <x:v>Verified CreateService on unused exact service and UpdateService on existing simple EC2 service, same active cluster and connected host, task definition revision and PassRole context; positive and negative cases in test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="O82" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -2259,10 +3657,27 @@
       <x:c r="E83" s="6" t="str"/>
       <x:c r="F83" s="6" t="str"/>
       <x:c r="G83" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H83" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I83" s="6" t="str"/>
+      <x:c r="J83" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K83" s="6" t="str"/>
+      <x:c r="L83" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M83" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N83" s="6" t="str">
+        <x:v>Verified StartTask and RegisterTaskDefinition on every new family revision, PassRole service context, exact same-Region cluster and active connected container instance; positive, wrong-host, missing-host, disconnected-host, denial cases in test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="O83" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -2283,10 +3698,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G84" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H84" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I84" s="6" t="str"/>
+      <x:c r="J84" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K84" s="6" t="str"/>
+      <x:c r="L84" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M84" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N84" s="6" t="str">
+        <x:v>Reviewed AWS TaskOverride, RunTask, task execution-role and PassRole documentation against the current evaluator. A conditional role path requires one described ACTIVE EC2-compatible task definition with a named image container, an ACTIVE same-Region cluster with registered container capacity, scoped ecs:RunTask on the exact definition with its ecs:cluster context, and iam:PassRole for the target task role and any separate execution role with iam:PassedToService=ecs-tasks.amazonaws.com. Direct positive and wrong task, wrong cluster, wrong service, missing execution-role grant, inactive definition, zero-capacity and Fargate cases pass in tests/test_peaso_privesc_aws_followups.py. Fargate and awsvpc definitions stay UNKNOWN until network and launch facts are joined; image pull, command handling and placement remain explicit runtime conditions, so a conditional edge does not claim the task executed. AWS references: https://docs.aws.amazon.com/AmazonECS/latest/APIReference/API_TaskOverride.html and https://docs.aws.amazon.com/AmazonECS/latest/APIReference/API_RunTask.html.</x:v>
+      </x:c>
+      <x:c r="O84" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -2305,10 +3737,27 @@
       <x:c r="E85" s="6" t="str"/>
       <x:c r="F85" s="6" t="str"/>
       <x:c r="G85" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H85" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I85" s="6" t="str"/>
+      <x:c r="J85" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K85" s="6" t="str"/>
+      <x:c r="L85" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M85" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N85" s="6" t="str">
+        <x:v>Verified privileged registration, exact Linux EC2 host and role join, scoped StartTask, and single-host RunTask/CreateService/UpdateService; positive and wrong-host, disconnected, disabled-IMDS, policy-denied, multi-host cases in test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="O85" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -2327,10 +3776,27 @@
       <x:c r="E86" s="6" t="str"/>
       <x:c r="F86" s="6" t="str"/>
       <x:c r="G86" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H86" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I86" s="6" t="str"/>
+      <x:c r="J86" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K86" s="6" t="str"/>
+      <x:c r="L86" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M86" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N86" s="6" t="str">
+        <x:v>Verified active EXTERNAL service and connected EC2 capacity, scoped task-definition revisions, all generated task-set IDs, exact service promotion and PassRole context; positive and controller, host, service, revision, denial negatives in test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="O86" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -2351,10 +3817,27 @@
         <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="G87" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="H87" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
+      </x:c>
+      <x:c r="I87" s="6" t="str"/>
+      <x:c r="J87" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K87" s="6" t="str"/>
+      <x:c r="L87" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M87" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N87" s="6" t="str">
+        <x:v>Exact same-account file-system ARN, PutFileSystemPolicy, accepted self-naming policy, prior ClientMount denial and effective new authorization checked; missing/duplicate/mismatched evidence and nonwriter negatives; tests/test_peaso_privesc_aws_scoped_grants.py; AWS EFS Service Authorization Reference and PutFileSystemPolicy API</x:v>
+      </x:c>
+      <x:c r="O87" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -2375,10 +3858,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G88" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H88" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I88" s="6" t="str"/>
+      <x:c r="J88" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K88" s="6" t="str"/>
+      <x:c r="L88" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M88" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N88" s="6" t="str">
+        <x:v>Existing STANDARD entry joined to exact principal and cluster, access-entry ARN and policy/scope conditions; stale IAM identity remains conditional; tests/test_peaso_privesc_aws_followups.py; AWS EKS AssociateAccessPolicy and AccessEntry docs</x:v>
+      </x:c>
+      <x:c r="O88" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -2399,10 +3899,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G89" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H89" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I89" s="6" t="str"/>
+      <x:c r="J89" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K89" s="6" t="str"/>
+      <x:c r="L89" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M89" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N89" s="6" t="str">
+        <x:v>Collected API/API_AND_CONFIG_MAP cluster and complete access-entry inventory; no existing source entry; CreateAccessEntry on that cluster with exact source IAM principal and STANDARD type; AssociateAccessPolicy on the new source-entry ARN with AmazonEKSClusterAdminPolicy and cluster scope. Wrong cluster, policy, scope, principal, existing entry and missing collection negatives pass; endpoint reachability and new UUID remain conditional. tests/test_peaso_privesc_aws_followups.py; AWS EKS access-entry, authentication-mode and Service Authorization Reference docs.</x:v>
+      </x:c>
+      <x:c r="O89" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -2423,10 +3940,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G90" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H90" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I90" s="6" t="str"/>
+      <x:c r="J90" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K90" s="6" t="str"/>
+      <x:c r="L90" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M90" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N90" s="6" t="str">
+        <x:v>Collected ACTIVE CONFIG_MAP cluster with a Kubernetes/platform version eligible for EKS access entries; UpdateClusterConfig context requests API_AND_CONFIG_MAP; source IAM principal, absent self-entry, CreateAccessEntry and AssociateAccessPolicy are bound to the same cluster and cluster-wide AmazonEKSClusterAdminPolicy. Unsupported platform, UPDATING status, wrong mode/policy/scope and missing version negatives pass; update propagation and API endpoint reachability remain conditional. tests/test_peaso_privesc_aws_followups.py; AWS EKS Change authentication mode and Service Authorization Reference docs.</x:v>
+      </x:c>
+      <x:c r="O90" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -2447,10 +3981,27 @@
       </x:c>
       <x:c r="F91" s="6" t="str"/>
       <x:c r="G91" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_beanstalk_environment_role_effect.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H91" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_beanstalk_environment_role_effect.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I91" s="6" t="str"/>
+      <x:c r="J91" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K91" s="6" t="str"/>
+      <x:c r="L91" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M91" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N91" s="6" t="str">
+        <x:v>Current audit: AWS Elastic Beanstalk uses an application version and source bundle to deploy code to a created or updated environment, with an EC2 instance profile and a service role. The previous generic IAM requirements mixed unbound CloudFormation, EC2, Auto Scaling and S3 grants and could miss scoped permissions. The evaluator now needs a fresh reviewed accepted deployment: exact application/version/environment ARNs, source-uploaded readable same-Region bundle, service role readiness, launched instance, applied profile and immutable target role ID, executed source code and useful action unavailable directly to the caller. It checks CreateApplicationVersion on both exact resources, exact Create/UpdateEnvironment, optional CreateApplication, S3 PutObject and the recorded PassRole request context. Missing, stale or conflicting evidence remains unresolved. Create/update positives, disjoint grants, unexecuted code, wrong role/context, current and prior binding tests pass. AWS Elastic Beanstalk service roles, instance profiles, application-version API and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O91" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -2471,10 +4022,27 @@
         <x:v>tests/test_peaso_privesc_emr_existing_steps.py</x:v>
       </x:c>
       <x:c r="G92" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_emr_existing_steps.py</x:v>
       </x:c>
       <x:c r="H92" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_emr_existing_steps.py</x:v>
+      </x:c>
+      <x:c r="I92" s="6" t="str"/>
+      <x:c r="J92" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K92" s="6" t="str"/>
+      <x:c r="L92" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M92" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N92" s="6" t="str">
+        <x:v>Current review binds the exact active cluster, instance profile, target role and AddJobFlowSteps grant. Runtime-role-enabled clusters no longer imply instance-profile access; missing security configuration remains unknown. Positive and negative cases in tests/test_peaso_privesc_emr_existing_steps.py; AWS runtime-role and EMR security docs.</x:v>
+      </x:c>
+      <x:c r="O92" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -2493,10 +4061,27 @@
       <x:c r="E93" s="6" t="str"/>
       <x:c r="F93" s="6" t="str"/>
       <x:c r="G93" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H93" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I93" s="6" t="str"/>
+      <x:c r="J93" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K93" s="6" t="str"/>
+      <x:c r="L93" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M93" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N93" s="6" t="str">
+        <x:v>New runtime-role route joins an active cluster with runtime-role security configuration, its instance profile, host sts:AssumeRole and sts:TagSession, target trust and source AddJobFlowSteps with ExecutionRoleArn context. Conditional role use requires an accepted step. Focused positive, wrong-cluster, wrong-role, missing-host-AssumeRole/TagSession and disabled-config tests pass; AWS EMR runtime-role guide.</x:v>
+      </x:c>
+      <x:c r="O93" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -2517,10 +4102,27 @@
       </x:c>
       <x:c r="F94" s="6" t="str"/>
       <x:c r="G94" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_emr_containers_role_effect.py</x:v>
       </x:c>
       <x:c r="H94" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_emr_containers_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I94" s="6" t="str"/>
+      <x:c r="J94" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K94" s="6" t="str"/>
+      <x:c r="L94" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M94" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N94" s="6" t="str">
+        <x:v>Current audit: the route joins one ACTIVE endpoint of a RUNNING virtual cluster with matching EKS OIDC trust and exact GetManagedEndpointSessionCredentials authorization. A fresh reviewed proof must show the endpoint token issued, the endpoint connection succeeded, controlled interactive code executed under the immutable target role ID, and a useful action unavailable directly to the caller. The token is an endpoint credential, not STS keys. Missing, stale, duplicate, wrong-role or unreachable-endpoint evidence remains unresolved. Positive and negative, inventory and historical-binding tests pass. AWS EMR on EKS managed endpoint and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O94" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -2541,10 +4143,27 @@
       </x:c>
       <x:c r="F95" s="6" t="str"/>
       <x:c r="G95" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_emr_containers_role_effect.py</x:v>
       </x:c>
       <x:c r="H95" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_emr_containers_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I95" s="6" t="str"/>
+      <x:c r="J95" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K95" s="6" t="str"/>
+      <x:c r="L95" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M95" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N95" s="6" t="str">
+        <x:v>Current audit: the route joins a RUNNING virtual cluster, matching ACTIVE EKS OIDC issuer and namespace, exact StartJobRun authorization, and a fresh reviewed accepted job run that executed source-controlled readable code under the immutable target role ID. PassRole uses the recorded service and associated-resource context; the role performed a useful action unavailable directly to the caller. Missing, stale, duplicate, wrong-role or unreadable-artifact evidence remains unresolved. Scoped positive and negative tests, prior binding, OIDC trust and inventory regressions pass. AWS EMR on EKS execution-role guide, StartJobRun API and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O95" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -2565,10 +4184,27 @@
       </x:c>
       <x:c r="F96" s="6" t="str"/>
       <x:c r="G96" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_emr_containers_role_effect.py</x:v>
       </x:c>
       <x:c r="H96" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_emr_containers_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I96" s="6" t="str"/>
+      <x:c r="J96" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K96" s="6" t="str"/>
+      <x:c r="L96" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M96" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N96" s="6" t="str">
+        <x:v>Current audit: the route joins a RUNNING virtual cluster, ACTIVE EKS cluster, all three matching client/driver/executor Pod Identity associations, exact StartJobRun and PassRole scoped to pods.eks.amazonaws.com and the EKS cluster ARN. A fresh reviewed job run must establish a supported release, ready agent, readable controlled code, applied immutable role ID, code execution and a useful role action unavailable directly to the caller. Missing, stale, wrong-role, missing-agent or unexecuted evidence stays unresolved. Positive and negative, association, trust and prior-binding tests pass. AWS EMR on EKS Pod Identity setup and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O96" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -2589,10 +4225,29 @@
       </x:c>
       <x:c r="F97" s="6" t="str"/>
       <x:c r="G97" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_api_evidence_static_20261020.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_emr_cluster_endpoint_role_effect.py</x:v>
       </x:c>
       <x:c r="H97" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_api_evidence_static_20261020.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_emr_cluster_endpoint_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I97" s="6" t="str"/>
+      <x:c r="J97" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K97" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_emr_cluster_endpoint_role_effect.py</x:v>
+      </x:c>
+      <x:c r="L97" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M97" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N97" s="6" t="str">
+        <x:v>Current audit: AWS GetClusterSessionCredentials returns temporary HTTP basic credentials for compatible EMR cluster endpoints, not AWS STS keys. Existing cluster/runtime-role joins still require the running cluster, role-enabled security configuration, exact GetClusterSessionCredentials permission with ExecutionRoleArn context, instance-profile host role AssumeRole and TagSession rights, and matching runtime-role trust. A concrete edge now additionally requires fresh reviewed credentials issued for that exact cluster, endpoint authentication and reachable interactive workload execution under the immutable runtime role ID, and a useful role action unavailable directly to source. Missing, stale, conflicting, wrong-role or unexecuted evidence remains unresolved. Positive and negative tests, legacy guard, current/prior catalog binding and sync pass. AWS GetClusterSessionCredentials API and EMR runtime-role guide.</x:v>
+      </x:c>
+      <x:c r="O97" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -2613,10 +4268,27 @@
       </x:c>
       <x:c r="F98" s="6" t="str"/>
       <x:c r="G98" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_emr_new_cluster_role_effect.py</x:v>
       </x:c>
       <x:c r="H98" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_emr_new_cluster_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I98" s="6" t="str"/>
+      <x:c r="J98" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K98" s="6" t="str"/>
+      <x:c r="L98" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M98" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N98" s="6" t="str">
+        <x:v>Current audit: RunJobFlow and separate PassRole grants for the exact EC2 instance role and EMR service role are checked with reviewed request context. A concrete edge needs fresh accepted launch evidence binding the service and instance RoleIds, applied instance profile and member instance, controlled bootstrap or step execution, and a useful role action unavailable to the caller. Optional Auto Scaling and Spot dependencies must be ready when requested. Missing execution, wrong profile, stale or missing evidence, and missing service PassRole stay unresolved. Focused positive/negative tests and historical catalog binding pass; AWS EMR role, RunJobFlow and bootstrap documentation.</x:v>
+      </x:c>
+      <x:c r="O98" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -2637,10 +4309,27 @@
       </x:c>
       <x:c r="F99" s="6" t="str"/>
       <x:c r="G99" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_emr_serverless_route.py</x:v>
       </x:c>
       <x:c r="H99" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_emr_serverless_route.py</x:v>
+      </x:c>
+      <x:c r="I99" s="6" t="str"/>
+      <x:c r="J99" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K99" s="6" t="str"/>
+      <x:c r="L99" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M99" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N99" s="6" t="str">
+        <x:v>Current audit: AWS EMR Serverless StartJobRun can use a passed runtime role on a runnable same-account application. The old evaluator emitted a conditional role edge from IAM grants and a guessed S3 script object even though no job execution was observed; it also could miss PassRole policies scoped with iam:AssociatedResourceArn. The new route joins a fresh reviewed accepted job run, exact application and immutable role ID, source-controlled readable artifact, executed code using role credentials, and a useful action unavailable directly to source. For an S3 artifact it checks source PutObject and target GetObject on the exact object; PassRole uses reviewed service and associated-resource context. Absent, stale or mismatched execution proof remains unresolved. Positive, negative, scoped PassRole, prior/current binding and sync tests pass. AWS EMR Serverless JobRun API, runtime-role and IAM documentation.</x:v>
+      </x:c>
+      <x:c r="O99" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -2661,10 +4350,27 @@
       </x:c>
       <x:c r="F100" s="6" t="str"/>
       <x:c r="G100" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_events_subscriber_effect.py</x:v>
       </x:c>
       <x:c r="H100" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_events_subscriber_effect.py</x:v>
+      </x:c>
+      <x:c r="I100" s="6" t="str"/>
+      <x:c r="J100" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K100" s="6" t="str"/>
+      <x:c r="L100" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M100" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N100" s="6" t="str">
+        <x:v>Current audit: exact active custom bus, CreateSubscriber on the bus and new subscriber name/* ARN, PutEvents on that bus, and PassRole to events.amazonaws.com are required. One fresh reviewed witness must bind the accepted universal target, its supported write action and exact resource, a matching published event, successful delivery under the immutable role ID, and a useful effect unavailable directly to the caller. A policy scoped only to a completed subscriber ARN, undelivered or read-only targets, and customer KMS buses without key proof remain unresolved. Focused positive/negative tests and historical catalog binding pass; AWS custom bus subscriber, access action and universal target docs.</x:v>
+      </x:c>
+      <x:c r="O100" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -2685,10 +4391,27 @@
         <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="G101" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="H101" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
+      </x:c>
+      <x:c r="I101" s="6" t="str"/>
+      <x:c r="J101" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K101" s="6" t="str"/>
+      <x:c r="L101" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M101" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N101" s="6" t="str">
+        <x:v>AWS Managed Flink CreateApplication accepts caller-supplied ZipFileContent, requires a ServiceExecutionRole, and StartApplication runs the submitted application; AWS documents that its SDK credentials come from that execution role. The Service Authorization Reference places CreateApplication on * and StartApplication on the application ARN with PassRole bound to kinesisanalytics.amazonaws.com. The evaluator chooses an unused collected application name, verifies CreateApplication, exact StartApplication and target PassRole, and leaves incomplete authorization or inventory unresolved. Focused positive, occupied-name, wrong-account, wrong-service and denied-inventory tests in tests/test_peaso_privesc_aws_ext_facts.py. Service quotas and malformed submitted code may stop a particular launch, so the edge remains conditional.</x:v>
+      </x:c>
+      <x:c r="O101" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -2709,10 +4432,27 @@
         <x:v>tests/test_peaso_privesc_flink_existing_studio.py</x:v>
       </x:c>
       <x:c r="G102" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_flink_existing_studio.py</x:v>
       </x:c>
       <x:c r="H102" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_flink_existing_studio.py</x:v>
+      </x:c>
+      <x:c r="I102" s="6" t="str"/>
+      <x:c r="J102" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K102" s="6" t="str"/>
+      <x:c r="L102" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M102" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N102" s="6" t="str">
+        <x:v>Exact RUNNING INTERACTIVE application ARN and recorded ServiceExecutionRole joined to application-scoped CreateApplicationPresignedUrl; collector projection retains both role and mode; positive and wrong-application/non-Studio/stopped/denied-inventory tests in tests/test_peaso_privesc_flink_existing_studio.py; AWS API and Studio documentation.</x:v>
+      </x:c>
+      <x:c r="O102" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -2731,10 +4471,27 @@
       <x:c r="E103" s="6" t="str"/>
       <x:c r="F103" s="6" t="str"/>
       <x:c r="G103" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_shared_role.py</x:v>
       </x:c>
       <x:c r="H103" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_shared_role.py</x:v>
+      </x:c>
+      <x:c r="I103" s="6" t="str"/>
+      <x:c r="J103" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K103" s="6" t="str"/>
+      <x:c r="L103" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M103" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N103" s="6" t="str">
+        <x:v>Exact active EC2 fleet and compute join, InstanceRoleArn and SHARED_CREDENTIAL_FILE are required. The source must have GetComputeAccess on that fleet ARN; runtime shell and file readability remain conditional. Missing inventory stays unresolved. Focused collector, permission, evaluator and historical-binding checks pass; AWS GetComputeAccess and fleet shared-credential docs.</x:v>
+      </x:c>
+      <x:c r="O103" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -2753,10 +4510,27 @@
       <x:c r="E104" s="6" t="str"/>
       <x:c r="F104" s="6" t="str"/>
       <x:c r="G104" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_shared_role.py</x:v>
       </x:c>
       <x:c r="H104" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_shared_role.py</x:v>
+      </x:c>
+      <x:c r="I104" s="6" t="str"/>
+      <x:c r="J104" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K104" s="6" t="str"/>
+      <x:c r="L104" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M104" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N104" s="6" t="str">
+        <x:v>Current catalog now requires source CreateBuild and CreateFleet in the same recorded Region plus effective PassRole for gamelift.amazonaws.com on the exact target role. CreateBuild without StorageLocation returns initial upload credentials, so the source can supply its own game build; fleet activation and runnable uploaded code remain conditional. Existing builds, scripts and container fleets remain unresolved rather than producing a concrete edge. Positive and negative checks cover Region separation, PassRole service restriction, missing CreateBuild and container-only permission. A follow-up requires global Resource authorization for CreateBuild, CreateFleet and CreateContainerFleet; grants scoped only to existing build or fleet ARNs no longer produce an edge. AWS CreateBuild/CreateFleet APIs and GameLift Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O104" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -2775,10 +4549,27 @@
       <x:c r="E105" s="6" t="str"/>
       <x:c r="F105" s="6" t="str"/>
       <x:c r="G105" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_admin_shell.py</x:v>
       </x:c>
       <x:c r="H105" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_admin_shell.py</x:v>
+      </x:c>
+      <x:c r="I105" s="6" t="str"/>
+      <x:c r="J105" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K105" s="6" t="str"/>
+      <x:c r="L105" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M105" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N105" s="6" t="str">
+        <x:v>AWS ListStreamGroups supplies exact parent-group status and ListStreamSessions supplies session ARN, status and RoleArn. AWS requires the parent group ACTIVE and session in one of four live states for an admin shell. The collector now retains the group status, marks absent status partial, and the evaluator requires ACTIVE before a conditional role edge. Exact group action authorization and role/session binding remain required; focused direct positive/negative collector and evaluator checks pass. The new YAML binds this condition and preserves the exact prior 682-entry catalog for stored results. The separate controlled-application StartStreamSession route remains unresolved.</x:v>
+      </x:c>
+      <x:c r="O105" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -2799,10 +4590,27 @@
       </x:c>
       <x:c r="F106" s="6" t="str"/>
       <x:c r="G106" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_admin_shell.py, tests/test_peaso_privesc_gameliftstreams_session_effect.py</x:v>
       </x:c>
       <x:c r="H106" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_gamelift_admin_shell.py, tests/test_peaso_privesc_gameliftstreams_session_effect.py</x:v>
+      </x:c>
+      <x:c r="I106" s="6" t="str"/>
+      <x:c r="J106" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K106" s="6" t="str"/>
+      <x:c r="L106" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M106" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N106" s="6" t="str">
+        <x:v>Current audit: StartStreamSession is checked on the exact stream group with gameliftstreams:RoleArn request context; CreateStreamUrl also needs the exact application and group plus its StartStreamSession dependency. PassRole must allow gameliftstreams.amazonaws.com. A fresh reviewed witness binds a compatible ACTIVE group with capacity, associated READY controlled application, accepted launch, connected session, executed code, issued session credentials and useful action under the immutable role ID unavailable to the caller. Unsupported group credentials, missing application authorization or failed code/action remain unresolved. Both positive routes and negative cases plus historical binding pass; AWS session credentials, StartStreamSession and Service Authorization Reference docs.</x:v>
+      </x:c>
+      <x:c r="O106" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -2821,10 +4629,27 @@
       <x:c r="E107" s="6" t="str"/>
       <x:c r="F107" s="6" t="str"/>
       <x:c r="G107" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_glue_script_object.py</x:v>
       </x:c>
       <x:c r="H107" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_glue_script_object.py</x:v>
+      </x:c>
+      <x:c r="I107" s="6" t="str"/>
+      <x:c r="J107" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K107" s="6" t="str"/>
+      <x:c r="L107" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M107" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N107" s="6" t="str">
+        <x:v>Exact collected Glue job ScriptLocation, attached role, source PutObject, role GetObject and same-job StartJobRun or active scheduled trigger are machine joined. Wrong object, job or role cannot bind; incomplete inventory and ambiguous URI stay unknown. Focused positive/negative tests and exact current/historical catalog binding pass. AWS Glue JobCommand and script editor docs. Glue argument precedence is checked: pinned --scriptLocation is unresolved, and scheduled runs require no script redirect in job defaults or trigger action arguments; only argument names are retained.</x:v>
+      </x:c>
+      <x:c r="O107" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -2843,10 +4668,27 @@
       <x:c r="E108" s="6" t="str"/>
       <x:c r="F108" s="6" t="str"/>
       <x:c r="G108" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_glue_new_dev_endpoint.py</x:v>
       </x:c>
       <x:c r="H108" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_glue_new_dev_endpoint.py</x:v>
+      </x:c>
+      <x:c r="I108" s="6" t="str"/>
+      <x:c r="J108" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K108" s="6" t="str"/>
+      <x:c r="L108" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M108" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N108" s="6" t="str">
+        <x:v>AWS Glue CreateDevEndpoint and GetDevEndpoints APIs plus Service Authorization Reference reviewed. The source must have global CreateDevEndpoint, exact iam:PassRole with iam:PassedToService=glue.amazonaws.com, and GetDevEndpoints or GetDevEndpoint on one unused generated endpoint in a collected supported Region. The target must trust Glue. Public SSH access, provisioning and quotas remain conditional; disabled or unsupported Regions and scoped grants to global actions do not produce an edge. Focused positive and negative tests and current/historical catalog binding pass.</x:v>
+      </x:c>
+      <x:c r="O108" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -2867,10 +4709,27 @@
       </x:c>
       <x:c r="F109" s="6" t="str"/>
       <x:c r="G109" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_glue_job_script_bind.py</x:v>
       </x:c>
       <x:c r="H109" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_glue_job_script_bind.py</x:v>
+      </x:c>
+      <x:c r="I109" s="6" t="str"/>
+      <x:c r="J109" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K109" s="6" t="str"/>
+      <x:c r="L109" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M109" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N109" s="6" t="str">
+        <x:v>Current audit: exact CreateJob or UpdateJob, PassRole to glue.amazonaws.com, and same-job execution remain required. A script already named by a collected job can establish a conditional route when the caller can PutObject and the target role can GetObject. Fresh reviewed evidence now also supports a different script object by binding the accepted job change, matching run, script read/execution, immutable role ID and a useful role action unavailable to the caller. Missing or mismatched evidence remains unresolved. Existing static and external-script positive/negative tests and historical binding pass; AWS CreateJob, JobUpdate and Glue script argument docs.</x:v>
+      </x:c>
+      <x:c r="O109" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2889,10 +4748,29 @@
       <x:c r="E110" s="6" t="str"/>
       <x:c r="F110" s="6" t="str"/>
       <x:c r="G110" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_new_workload_role_paths.py</x:v>
       </x:c>
       <x:c r="H110" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_new_workload_role_paths.py</x:v>
+      </x:c>
+      <x:c r="I110" s="6" t="str"/>
+      <x:c r="J110" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K110" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_new_workload_role_paths.py</x:v>
+      </x:c>
+      <x:c r="L110" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M110" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N110" s="6" t="str">
+        <x:v>Reviewed AWS Glue CreateSession/RunStatement API and Service Authorization Reference. The source must pass the exact Glue-trusting role and have CreateSession and RunStatement on one unused session ARN in a collected Region; GetStatement only reads output. Fixed a false negative: valid session IDs may contain spaces and other single-line UTF-8 characters, so the evaluator now follows the API byte limit instead of a narrow ASCII regex. Focused test passes for exact and wildcard same-session grants including a space, and rejects different IDs, occupied IDs and incomplete inventory.</x:v>
+      </x:c>
+      <x:c r="O110" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -2912,11 +4790,26 @@
       <x:c r="F111" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G111" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G111" s="6" t="str"/>
       <x:c r="H111" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I111" s="6" t="str"/>
+      <x:c r="J111" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K111" s="6" t="str"/>
+      <x:c r="L111" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M111" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N111" s="6" t="str">
+        <x:v>Ready recorded session joined to exact role and session ARN; RunStatement permission required on that ARN, no PassRole needed for an existing session; tests/test_peaso_privesc_schema_ext.py; AWS RunStatement API and Glue interactive-session IAM guide</x:v>
+      </x:c>
+      <x:c r="O111" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -2937,10 +4830,27 @@
       </x:c>
       <x:c r="F112" s="6" t="str"/>
       <x:c r="G112" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_glue_override_script_bind.py, tests/test_peaso_privesc_glue_script_object.py</x:v>
       </x:c>
       <x:c r="H112" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_glue_override_script_bind.py, tests/test_peaso_privesc_glue_script_object.py</x:v>
+      </x:c>
+      <x:c r="I112" s="6" t="str"/>
+      <x:c r="J112" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K112" s="6" t="str"/>
+      <x:c r="L112" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M112" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N112" s="6" t="str">
+        <x:v>Current audit: exact StartJobRun or scheduled CreateTrigger, an unpinned --scriptLocation and a caller-writable, role-readable S3 script remain required. Fresh reviewed evidence now supports a controlled script outside recorded job definitions when the same job actually ran it and performed a useful action under the immutable role ID. Incorrect job, pinned script, wrong object and role-identity mismatch stay unresolved. Static and external-script tests pass; AWS Glue job argument precedence, StartJobRun and CreateTrigger docs.</x:v>
+      </x:c>
+      <x:c r="O112" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -2960,11 +4870,26 @@
       <x:c r="F113" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G113" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G113" s="6" t="str"/>
       <x:c r="H113" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I113" s="6" t="str"/>
+      <x:c r="J113" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K113" s="6" t="str"/>
+      <x:c r="L113" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M113" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N113" s="6" t="str">
+        <x:v>Ready endpoint joined to exact role and endpoint ARN, public SSH address, free key slot, conditional network reachability; unnecessary GetDevEndpoint requirement removed; tests/test_peaso_privesc_schema_ext.py; AWS UpdateDevEndpoint API and Glue ARN guide</x:v>
+      </x:c>
+      <x:c r="O113" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -2985,10 +4910,27 @@
       </x:c>
       <x:c r="F114" s="6" t="str"/>
       <x:c r="G114" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_glue_updatejob_script_bind.py</x:v>
       </x:c>
       <x:c r="H114" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_glue_updatejob_script_bind.py</x:v>
+      </x:c>
+      <x:c r="I114" s="6" t="str"/>
+      <x:c r="J114" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K114" s="6" t="str"/>
+      <x:c r="L114" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M114" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N114" s="6" t="str">
+        <x:v>Current audit: UpdateJob on the exact existing job, PassRole to glue.amazonaws.com on its attached role, and a runnable trigger remain required. A recorded writable/readable script supports the static route; fresh reviewed evidence also supports another controlled S3 script after the update, trigger firing, matching run, script execution and useful role action under the immutable role ID. Missing or contradictory proof stays unresolved. Static and external-script tests pass; AWS JobUpdate and Glue Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O114" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -3009,10 +4951,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G115" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H115" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I115" s="6" t="str"/>
+      <x:c r="J115" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K115" s="6" t="str"/>
+      <x:c r="L115" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M115" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N115" s="6" t="str">
+        <x:v>Collected exact ACTIVE Grafana workspace and CreateWorkspaceApiKey authorization on its workspace ARN; Grafana major version below 12 is required. AWS API accepts keyRole ADMIN; versions 9-11 still permit API creation although the UI does not, correcting an outdated catalog condition. Version 12, nonactive and missing-version negatives pass; network reach and quotas remain conditional. tests/test_peaso_privesc_aws_followups.py; AWS CreateWorkspaceApiKey API and Grafana v10 API-key guide.</x:v>
+      </x:c>
+      <x:c r="O115" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -3033,10 +4992,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G116" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H116" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I116" s="6" t="str"/>
+      <x:c r="J116" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K116" s="6" t="str"/>
+      <x:c r="L116" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M116" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N116" s="6" t="str">
+        <x:v>Collected exact ACTIVE Grafana workspace with version 9 or later; both CreateWorkspaceServiceAccount with ADMIN role and CreateWorkspaceServiceAccountToken must authorize its ARN. Version 8, missing either action and nonmatching workspace negatives pass; token creation and network reach remain conditional. tests/test_peaso_privesc_aws_followups.py; AWS CreateWorkspaceServiceAccount, CreateWorkspaceServiceAccountToken and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O116" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -3057,10 +5033,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G117" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H117" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I117" s="6" t="str"/>
+      <x:c r="J117" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K117" s="6" t="str"/>
+      <x:c r="L117" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M117" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N117" s="6" t="str">
+        <x:v>Collected exact ACTIVE Grafana workspace and UpdateWorkspaceAuthentication authorization on its ARN; AWS API accepts SAML IdP metadata and an Admin group role mapping. Inactive workspace, missing status and wrong-action negatives pass. Attacker-controlled valid SAML metadata/assertions, propagation and endpoint reach remain conditional. tests/test_peaso_privesc_aws_followups.py; AWS UpdateWorkspaceAuthentication, SamlConfiguration and Service Authorization Reference.</x:v>
+      </x:c>
+      <x:c r="O117" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -3079,10 +5072,29 @@
       <x:c r="E118" s="6" t="str"/>
       <x:c r="F118" s="6" t="str"/>
       <x:c r="G118" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_iam_add_user_to_group.py</x:v>
       </x:c>
       <x:c r="H118" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_iam_add_user_to_group.py</x:v>
+      </x:c>
+      <x:c r="I118" s="6" t="str"/>
+      <x:c r="J118" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K118" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_iam_add_user_to_group.py</x:v>
+      </x:c>
+      <x:c r="L118" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M118" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N118" s="6" t="str">
+        <x:v>Verified AddUserToGroup targets the group ARN and new group policies combine with the user under boundary and SCP limits; exact self-policy edit, AdministratorAccess attachment, and newly assumable role are conditional paths; quota, already-held permissions, non-IAM source, and unproven generic gains remain blocked or unknown; five focused cases pass</x:v>
+      </x:c>
+      <x:c r="O118" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -3102,11 +5114,26 @@
       <x:c r="F119" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G119" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G119" s="6" t="str"/>
       <x:c r="H119" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I119" s="6" t="str"/>
+      <x:c r="J119" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K119" s="6" t="str"/>
+      <x:c r="L119" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M119" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N119" s="6" t="str">
+        <x:v>Exact group membership and group ARN, AdministratorAccess or verified equivalent managed policy ARN under iam:PolicyARN, attachment quota and permissions boundary reviewed; missing GroupList or missing group inventory now unresolved rather than absent; tests/test_peaso_privesc_schema_ext.py; AWS IAM AttachGroupPolicy and iam:PolicyARN documentation</x:v>
+      </x:c>
+      <x:c r="O119" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -3126,11 +5153,26 @@
       <x:c r="F120" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G120" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G120" s="6" t="str"/>
       <x:c r="H120" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I120" s="6" t="str"/>
+      <x:c r="J120" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K120" s="6" t="str"/>
+      <x:c r="L120" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M120" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N120" s="6" t="str">
+        <x:v>Exact source role ARN, AdministratorAccess or verified equivalent managed policy ARN under iam:PolicyARN, already-attached policy, attachment quota, detach path and permissions boundary reviewed; tests/test_peaso_privesc_schema_ext.py; AWS IAM AttachRolePolicy and iam:PolicyARN documentation</x:v>
+      </x:c>
+      <x:c r="O120" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -3150,11 +5192,26 @@
       <x:c r="F121" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G121" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G121" s="6" t="str"/>
       <x:c r="H121" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I121" s="6" t="str"/>
+      <x:c r="J121" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K121" s="6" t="str"/>
+      <x:c r="L121" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M121" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N121" s="6" t="str">
+        <x:v>Exact source IAM user ARN, AdministratorAccess or verified equivalent managed policy ARN under iam:PolicyARN, already-attached policy, attachment quota, detach path, permissions boundary and readonly-only condition reviewed; tests/test_peaso_privesc_schema_ext.py; AWS IAM AttachUserPolicy and iam:PolicyARN documentation</x:v>
+      </x:c>
+      <x:c r="O121" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -3175,10 +5232,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G122" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc.py</x:v>
       </x:c>
       <x:c r="H122" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I122" s="6" t="str"/>
+      <x:c r="J122" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K122" s="6" t="str"/>
+      <x:c r="L122" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M122" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N122" s="6" t="str">
+        <x:v>CreateAccessKey must cover the exact same-account target IAM user and a recorded free access-key slot; a full two-key user requires both DeleteAccessKey and ListAccessKeys on that user to learn an existing key ID, while deletion alone or missing key inventory remains unresolved rather than a concrete path. Wrong-target and capacity regressions pass in tests/test_peaso_privesc_schema_ext.py; AWS CreateAccessKey, DeleteAccessKey and ListAccessKeys APIs</x:v>
+      </x:c>
+      <x:c r="O122" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -3199,10 +5273,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G123" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_attack_detection_aws_login_profile_next.py</x:v>
       </x:c>
       <x:c r="H123" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_attack_detection_aws_login_profile_next.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I123" s="6" t="str"/>
+      <x:c r="J123" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K123" s="6" t="str"/>
+      <x:c r="L123" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M123" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N123" s="6" t="str">
+        <x:v>CreateLoginProfile must authorize the exact same-account target user, whose collected login-profile state is absent and MFA device count is zero; existing password or MFA blocks a concrete console takeover and missing state is unresolved. Positive and negative cases pass in tests/test_peaso_privesc_schema_ext.py; AWS CreateLoginProfile and GetLoginProfile APIs</x:v>
+      </x:c>
+      <x:c r="O123" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3222,11 +5313,26 @@
       <x:c r="F124" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G124" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G124" s="6" t="str"/>
       <x:c r="H124" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I124" s="6" t="str"/>
+      <x:c r="J124" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K124" s="6" t="str"/>
+      <x:c r="L124" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M124" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N124" s="6" t="str">
+        <x:v>Joined assumable role and attached customer-managed policy; unrelated missing policy false negative fixed; tests/test_peaso_privesc_schema_ext.py; AWS CreatePolicyVersion API</x:v>
+      </x:c>
+      <x:c r="O124" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -3246,11 +5352,26 @@
       <x:c r="F125" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G125" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G125" s="6" t="str"/>
       <x:c r="H125" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I125" s="6" t="str"/>
+      <x:c r="J125" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K125" s="6" t="str"/>
+      <x:c r="L125" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M125" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N125" s="6" t="str">
+        <x:v>Exact attached customer-managed policy ARN, source write permission on same ARN, four-version capacity or DeletePolicyVersion for a full five-version policy, SetAsDefault availability, source permissions boundary, and missing group membership unknown reviewed; tests/test_peaso_privesc_schema_ext.py; AWS IAM CreatePolicyVersion API and policy versioning guide</x:v>
+      </x:c>
+      <x:c r="O125" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -3270,11 +5391,26 @@
       <x:c r="F126" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G126" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G126" s="6" t="str"/>
       <x:c r="H126" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I126" s="6" t="str"/>
+      <x:c r="J126" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K126" s="6" t="str"/>
+      <x:c r="L126" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M126" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N126" s="6" t="str">
+        <x:v>CreateRole without a forced boundary, inline PutRolePolicy or administrator-equivalent AttachRolePolicy, one available same-account role ARN, caller-trusting role and effective AssumeRole path checked; disjoint wildcard scopes, occupied names, explicit AssumeRole denial, boundary/attachment conditions and recorded full RolesQuota negatives or unresolved deletion checked; tests/test_peaso_privesc_schema_ext.py; AWS IAM CreateRole, GetAccountSummary, policy attachment and trust documentation</x:v>
+      </x:c>
+      <x:c r="O126" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -3295,10 +5431,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G127" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H127" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I127" s="6" t="str"/>
+      <x:c r="J127" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K127" s="6" t="str"/>
+      <x:c r="L127" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M127" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N127" s="6" t="str">
+        <x:v>CreateSAMLProvider must authorize the exact missing provider ARN named by a same-account role trust allowing sts:AssumeRoleWithSAML; collected provider inventory distinguishes missing from present and incomplete inventory stays unresolved; present-provider and wrong-ARN negatives pass in tests/test_peaso_privesc_schema_ext.py; AWS DeleteSAMLProvider API confirms deletion leaves the role trust reference</x:v>
+      </x:c>
+      <x:c r="O127" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -3318,11 +5471,26 @@
       <x:c r="F128" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G128" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G128" s="6" t="str"/>
       <x:c r="H128" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I128" s="6" t="str"/>
+      <x:c r="J128" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K128" s="6" t="str"/>
+      <x:c r="L128" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M128" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N128" s="6" t="str">
+        <x:v>Create and Reset need target-scoped grants and a supported service with target permission; collected credential slots, ID, Active/Inactive state and matching service are enforced. Delete and Update service-name conditions now bind to the same service, preventing missed two-slot and inactive-key routes; wrong-service test negative. Conditional outcome preserves API-key service scope and does not claim whole-user impersonation; tests/test_peaso_privesc_schema_ext.py; AWS IAM API keys guide, IAM service-name condition-key guide and ResetServiceSpecificCredential API.</x:v>
+      </x:c>
+      <x:c r="O128" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -3343,10 +5511,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G129" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H129" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I129" s="6" t="str"/>
+      <x:c r="J129" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K129" s="6" t="str"/>
+      <x:c r="L129" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M129" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N129" s="6" t="str">
+        <x:v>CreateUser, CreateAccessKey and inline PutUserPolicy or administrator-equivalent AttachUserPolicy must authorize one available user ARN in the source partition/account; disjoint wildcard paths and ReadOnlyAccess-only attachment are rejected; recorded full user quota blocks creation unless deletion remains unresolved; tests/test_peaso_privesc_schema_ext.py; AWS IAM CreateUser, CreateAccessKey and iam:PolicyARN documentation</x:v>
+      </x:c>
+      <x:c r="O129" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -3366,11 +5551,26 @@
       <x:c r="F130" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G130" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G130" s="6" t="str"/>
       <x:c r="H130" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I130" s="6" t="str"/>
+      <x:c r="J130" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K130" s="6" t="str"/>
+      <x:c r="L130" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M130" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N130" s="6" t="str">
+        <x:v>Exact target user requires recorded active MFA, DeactivateMFADevice on that user and a CreateLoginProfile or UpdateLoginProfile permission matching its recorded password state; zero MFA, wrong password branch and missing deactivation are rejected, while incomplete credential state remains unresolved; tests/test_peaso_privesc_schema_ext.py; AWS DeactivateMFADevice, CreateLoginProfile and UpdateLoginProfile APIs</x:v>
+      </x:c>
+      <x:c r="O130" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -3390,11 +5590,26 @@
       <x:c r="F131" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G131" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G131" s="6" t="str"/>
       <x:c r="H131" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I131" s="6" t="str"/>
+      <x:c r="J131" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K131" s="6" t="str"/>
+      <x:c r="L131" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M131" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N131" s="6" t="str">
+        <x:v>CreateVirtualMFADevice must authorize one concrete, unused, valid device ARN in the source account; occupied exact names are rejected and incomplete virtual MFA inventory stays unresolved. EnableMFADevice must cover the target user, its MFA slot must be available or removable, and at least one access-key or password route must fit recorded credential state; replacing a full key set requires both DeleteAccessKey and ListAccessKeys. Narrow resource grants, occupied name and missing inventory regressions pass in tests/test_peaso_privesc_schema_ext.py; AWS CreateVirtualMFADevice, ListVirtualMFADevices, EnableMFADevice and ListAccessKeys APIs</x:v>
+      </x:c>
+      <x:c r="O131" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3415,10 +5630,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G132" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_followups.py</x:v>
       </x:c>
       <x:c r="H132" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_followups.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I132" s="6" t="str"/>
+      <x:c r="J132" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K132" s="6" t="str"/>
+      <x:c r="L132" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M132" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N132" s="6" t="str">
+        <x:v>An existing role must be assumable by the source, the same role must allow PutRolePolicy or administrator-equivalent AttachRolePolicy, and its boundary, attached-policy quota, SCPs and existing explicit Deny statements must permit account administration. An inline Deny needs overwrite/delete permission and a managed Deny needs DetachRolePolicy for that exact policy ARN; wrong policy context, restrictive boundary and explicit AssumeRole Deny negatives pass alongside Attach and Put positives in tests/test_peaso_privesc_schema_ext.py; AWS IAM trust, permission-boundary and policy attachment documentation</x:v>
+      </x:c>
+      <x:c r="O132" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -3438,11 +5670,26 @@
       <x:c r="F133" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G133" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G133" s="6" t="str"/>
       <x:c r="H133" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I133" s="6" t="str"/>
+      <x:c r="J133" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K133" s="6" t="str"/>
+      <x:c r="L133" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M133" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N133" s="6" t="str">
+        <x:v>Group membership and matching group write scope; tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="O133" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -3462,11 +5709,26 @@
       <x:c r="F134" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G134" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G134" s="6" t="str"/>
       <x:c r="H134" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I134" s="6" t="str"/>
+      <x:c r="J134" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K134" s="6" t="str"/>
+      <x:c r="L134" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M134" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N134" s="6" t="str">
+        <x:v>Same-role write scope and other-role negative case; tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="O134" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -3486,11 +5748,26 @@
       <x:c r="F135" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G135" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G135" s="6" t="str"/>
       <x:c r="H135" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I135" s="6" t="str"/>
+      <x:c r="J135" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K135" s="6" t="str"/>
+      <x:c r="L135" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M135" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N135" s="6" t="str">
+        <x:v>Same-user write scope, boundary behavior, and other-user negative case; tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="O135" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -3510,11 +5787,26 @@
       <x:c r="F136" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G136" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G136" s="6" t="str"/>
       <x:c r="H136" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I136" s="6" t="str"/>
+      <x:c r="J136" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K136" s="6" t="str"/>
+      <x:c r="L136" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M136" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N136" s="6" t="str">
+        <x:v>DeleteSAMLProvider and CreateSAMLProvider must both authorize the same existing provider ARN named by a same-account role trust allowing sts:AssumeRoleWithSAML; a permission on only a missing or different provider does not create a concrete path; tests/test_peaso_privesc_schema_ext.py; AWS DeleteSAMLProvider and CreateSAMLProvider APIs</x:v>
+      </x:c>
+      <x:c r="O136" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -3534,11 +5826,26 @@
       <x:c r="F137" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G137" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G137" s="6" t="str"/>
       <x:c r="H137" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I137" s="6" t="str"/>
+      <x:c r="J137" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K137" s="6" t="str"/>
+      <x:c r="L137" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M137" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N137" s="6" t="str">
+        <x:v>Exact attached customer-managed policy ARN and source SetDefaultPolicyVersion permission on same ARN; a collected non-default admin-equivalent document required, read-only alternate and missing group membership negatives/unknown reviewed; tests/test_peaso_privesc_schema_ext.py; AWS IAM SetDefaultPolicyVersion API and policy versioning guide</x:v>
+      </x:c>
+      <x:c r="O137" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -3558,11 +5865,26 @@
       <x:c r="F138" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G138" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G138" s="6" t="str"/>
       <x:c r="H138" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I138" s="6" t="str"/>
+      <x:c r="J138" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K138" s="6" t="str"/>
+      <x:c r="L138" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M138" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N138" s="6" t="str">
+        <x:v>UpdateAssumeRolePolicy must authorize the exact same-account target role; a rewritten trust can name the source directly, but service-linked roles, an explicit AssumeRole deny, restrictive source boundary and wrong role ARN are rejected. The specific AWS role-trust guide says a user permissions boundary must allow sts:AssumeRole even when the user is named in the trust policy; positive and negative cases pass in tests/test_peaso_privesc_schema_ext.py; AWS Update a role trust policy and AssumeRole documentation</x:v>
+      </x:c>
+      <x:c r="O138" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3583,10 +5905,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G139" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_attack_detection_aws_login_profile_next.py</x:v>
       </x:c>
       <x:c r="H139" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_attack_detection_aws_login_profile_next.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I139" s="6" t="str"/>
+      <x:c r="J139" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K139" s="6" t="str"/>
+      <x:c r="L139" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M139" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N139" s="6" t="str">
+        <x:v>UpdateLoginProfile must authorize the exact same-account target user, whose collected login-profile state is present and MFA device count is zero; absent password or MFA blocks a concrete console takeover and missing state is unresolved. Positive and negative cases pass in tests/test_peaso_privesc_schema_ext.py; AWS UpdateLoginProfile and GetLoginProfile APIs</x:v>
+      </x:c>
+      <x:c r="O139" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -3606,11 +5945,26 @@
       <x:c r="F140" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G140" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G140" s="6" t="str"/>
       <x:c r="H140" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I140" s="6" t="str"/>
+      <x:c r="J140" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K140" s="6" t="str"/>
+      <x:c r="L140" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M140" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N140" s="6" t="str">
+        <x:v>UpdateSAMLProvider must cover the exact existing provider named by a same-account role trust that allows sts:AssumeRoleWithSAML; wrong action, explicit trust Deny, permission on another provider and absent existing-provider evidence do not produce a concrete path; tests/test_peaso_privesc_schema_ext.py; AWS UpdateSAMLProvider API and IAM SAML federation guide</x:v>
+      </x:c>
+      <x:c r="O140" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -3630,11 +5984,26 @@
       <x:c r="F141" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G141" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G141" s="6" t="str"/>
       <x:c r="H141" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I141" s="6" t="str"/>
+      <x:c r="J141" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K141" s="6" t="str"/>
+      <x:c r="L141" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M141" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N141" s="6" t="str">
+        <x:v>UploadSSHPublicKey must cover the exact target IAM user, whose recorded policies allow CodeCommit GitPull or GitPush and whose collected SSH-key count is below the five-key limit; a full set needs both DeleteSSHPublicKey and ListSSHPublicKeys, and missing key inventory stays unresolved. The collector now records SSH-key metadata and the customer read policy includes ListSSHPublicKeys; empty/full/list/delete and missing policy or inventory regressions pass in tests/test_peaso_privesc_schema_ext.py; AWS UploadSSHPublicKey and IAM quotas documentation</x:v>
+      </x:c>
+      <x:c r="O141" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3653,10 +6022,27 @@
       <x:c r="E142" s="6" t="str"/>
       <x:c r="F142" s="6" t="str"/>
       <x:c r="G142" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_facts_followups.py, tests/test_peaso_privesc_imagebuilder_pipeline_binding.py</x:v>
       </x:c>
       <x:c r="H142" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_facts_followups.py, tests/test_peaso_privesc_imagebuilder_pipeline_binding.py</x:v>
+      </x:c>
+      <x:c r="I142" s="6" t="str"/>
+      <x:c r="J142" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K142" s="6" t="str"/>
+      <x:c r="L142" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M142" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N142" s="6" t="str">
+        <x:v>Current review found cross-pipeline permission mixing and false exclusion of semantic-version references without build number. The canonical YAML now uses a source precondition joining collected recipe component, exact pipeline and target profile role to broad CreateComponent authority over a future matching version/build and StartImagePipelineExecution on that same pipeline. Pinned builds are excluded; missing recipe and narrow fixed-build policies remain unresolved. Six focused tests pass, including exact prior catalog binding. AWS Image Builder semantic versioning, CreateComponent and service authorization docs.</x:v>
+      </x:c>
+      <x:c r="O142" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -3677,10 +6063,27 @@
       </x:c>
       <x:c r="F143" s="6" t="str"/>
       <x:c r="G143" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_exact_principal_tranche.py</x:v>
       </x:c>
       <x:c r="H143" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_exact_principal_tranche.py</x:v>
+      </x:c>
+      <x:c r="I143" s="6" t="str"/>
+      <x:c r="J143" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K143" s="6" t="str"/>
+      <x:c r="L143" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M143" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N143" s="6" t="str">
+        <x:v>Current audit: collector now lists each existing role alias and describes the exact IAM role it targets; customer setup includes iot:DescribeRoleAlias. A concrete edge requires fresh full-principal attestation binding the target role, an attacker-held ACTIVE certificate registered without a CA, AttachPolicy on that exact certificate, a policy permitting AssumeRoleWithCertificate on the inventoried alias, and successful credential-provider authentication. Current authorization fingerprint and unrestricted usable role credentials are mandatory. Wrong target, denied alias detail, malformed certificate and stale or scoped credentials stay unresolved. Positive/negative contract, collector and permission tests pass; AWS IoT credential-provider and DescribeRoleAlias docs.</x:v>
+      </x:c>
+      <x:c r="O143" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -3699,10 +6102,27 @@
       <x:c r="E144" s="6" t="str"/>
       <x:c r="F144" s="6" t="str"/>
       <x:c r="G144" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_iot_role_alias.py</x:v>
       </x:c>
       <x:c r="H144" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_iot_role_alias.py</x:v>
+      </x:c>
+      <x:c r="I144" s="6" t="str"/>
+      <x:c r="J144" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K144" s="6" t="str"/>
+      <x:c r="L144" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M144" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N144" s="6" t="str">
+        <x:v>Current self-contained new-alias/new-policy route reviewed against both IoT source pages and AWS IoT Service Authorization Reference. Requires exact iam:PassRole on the target with PassedToService=iot.amazonaws.com, target trust for credentials.iot.amazonaws.com, and one common Region for a fresh alias, fresh IoT policy, broad attachment to a new certificate and either global certificate creation or registration. New alias/policy name permissions must contain wildcard room; one fixed existing certificate grant is insufficient. Focused tests cover both positive certificate routes, disjoint Regions, missing grants, wrong service/trust and historical catalog bindings. The existing-alias/new-policy/new-certificate route is a separate active entry; existing-policy and already-held certificate alternatives remain unresolved.</x:v>
+      </x:c>
+      <x:c r="O144" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -3723,10 +6143,27 @@
       </x:c>
       <x:c r="F145" s="6" t="str"/>
       <x:c r="G145" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_exact_principal_tranche.py</x:v>
       </x:c>
       <x:c r="H145" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_exact_principal_tranche.py</x:v>
+      </x:c>
+      <x:c r="I145" s="6" t="str"/>
+      <x:c r="J145" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K145" s="6" t="str"/>
+      <x:c r="L145" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M145" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N145" s="6" t="str">
+        <x:v>Current audit: the existing alias must resolve to the exact target role through DescribeRoleAlias. The attestation binds CreateProvisioningTemplate and CreateProvisioningClaim to the same template, PassRole with iam:PassedToService=iot.amazonaws.com to a distinct provisioning role, the claim used over MQTT, a permanent ACTIVE certificate and its policy, and successful credential-provider authentication. The full-principal fingerprint and usable unrestricted role session are mandatory; wrong alias, template, role or incomplete evidence remains unresolved. Positive/negative contract, collector and customer-permission tests pass; AWS IoT provisioning and credential-provider docs.</x:v>
+      </x:c>
+      <x:c r="O145" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -3745,10 +6182,27 @@
       <x:c r="E146" s="6" t="str"/>
       <x:c r="F146" s="6" t="str"/>
       <x:c r="G146" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_iot_role_alias.py</x:v>
       </x:c>
       <x:c r="H146" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_iot_role_alias.py</x:v>
+      </x:c>
+      <x:c r="I146" s="6" t="str"/>
+      <x:c r="J146" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K146" s="6" t="str"/>
+      <x:c r="L146" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M146" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N146" s="6" t="str">
+        <x:v>Added exact existing-alias route after AWS ListRoleAliases and UpdateRoleAlias review. The read-only collector records a same-Region alias name and ARN, and the evaluator requires UpdateRoleAlias on that exact ARN, PassRole on the target with iot.amazonaws.com service context, target trust for credentials.iot.amazonaws.com, a creatable IoT policy, AttachPolicy on a new certificate and either certificate creation or self-registration in the same Region. Missing or denied alias inventory stays unresolved; another alias or a disjoint policy Region yields no definite role edge. Focused positive/negative collector, evaluator and old-binding tests pass. Existing policy and already-held certificate alternatives still need separate joins.</x:v>
+      </x:c>
+      <x:c r="O146" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -3769,10 +6223,27 @@
       </x:c>
       <x:c r="F147" s="6" t="str"/>
       <x:c r="G147" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_kafkaconnect_effect.py, tests/test_peaso_privesc_kafkaconnect_guard.py</x:v>
       </x:c>
       <x:c r="H147" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_kafkaconnect_effect.py, tests/test_peaso_privesc_kafkaconnect_guard.py</x:v>
+      </x:c>
+      <x:c r="I147" s="6" t="str"/>
+      <x:c r="J147" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K147" s="6" t="str"/>
+      <x:c r="L147" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M147" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N147" s="6" t="str">
+        <x:v>Current audit: CreateConnector and CreateCustomPlugin are checked on their global authorization resource, with PassRole scoped to kafkaconnect.amazonaws.com on the exact service execution role. A concrete edge additionally needs fresh reviewed evidence joining a source-controlled S3 JAR or ZIP, its created custom plugin, the connector selecting that plugin, reachable Kafka and working network setup, running plugin code, immutable role ID and a useful action unavailable to the caller. Missing plugin execution, wrong plugin, stale evidence and wrong PassRole service cannot create a role edge. Positive/negative tests, historical binding and sync pass; AWS MSK Connect API, Service Authorization Reference and plugin guide.</x:v>
+      </x:c>
+      <x:c r="O147" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -3791,10 +6262,29 @@
       <x:c r="E148" s="6" t="str"/>
       <x:c r="F148" s="6" t="str"/>
       <x:c r="G148" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
       </x:c>
       <x:c r="H148" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
+      </x:c>
+      <x:c r="I148" s="6" t="str"/>
+      <x:c r="J148" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K148" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
+      </x:c>
+      <x:c r="L148" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M148" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N148" s="6" t="str">
+        <x:v>Verified Lambda code-signing APIs and authorization resources. The evaluator joins UpdateFunctionCode and InvokeFunction on one active supported ZIP function with enforced signing, checks Delete on that function ARN, Put on a recorded Warn config ARN, UpdateCodeSigningConfig on the attached config ARN, or Create plus broad Put for a generated Warn config using a recorded publisher. Missing invocation, config or scope evidence remains unknown. Positive and negative focused cases, strict schema and syntax checks pass.</x:v>
+      </x:c>
+      <x:c r="O148" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -3817,10 +6307,27 @@
         <x:v>tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
       </x:c>
       <x:c r="G149" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_schema_v3_aws.py, tests/test_peaso_privesc_v4_all_id_proofs.py, tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
       </x:c>
       <x:c r="H149" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_v3_aws.py, tests/test_peaso_privesc_v4_all_id_proofs.py, tests/test_peaso_privesc_v4_exact_user_credentials.py</x:v>
+      </x:c>
+      <x:c r="I149" s="6" t="str"/>
+      <x:c r="J149" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K149" s="6" t="str"/>
+      <x:c r="L149" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M149" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N149" s="6" t="str">
+        <x:v>GetFunctionConfiguration exact function ARN, same partition/account/Region, reviewed successful plaintext credential read (including effective KMS access where needed), user authentication, and exact newly allowed action/resource required; missing, false, conflicting and wrong-resource negatives; tests/test_peaso_privesc_v4_exact_user_credentials.py and test_peaso_privesc_v4_all_id_proofs.py; AWS Lambda API and environment encryption guide</x:v>
+      </x:c>
+      <x:c r="O149" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -3841,10 +6348,27 @@
         <x:v>tests/test_peaso_privesc_lambda_microvm_connector.py</x:v>
       </x:c>
       <x:c r="G150" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_microvm_connector.py</x:v>
       </x:c>
       <x:c r="H150" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_microvm_connector.py</x:v>
+      </x:c>
+      <x:c r="I150" s="6" t="str"/>
+      <x:c r="J150" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K150" s="6" t="str"/>
+      <x:c r="L150" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M150" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N150" s="6" t="str">
+        <x:v>Current audit: AWS Lambda MicroVM security, networking, RunMicrovm API, service authorization and IAM PassRole condition docs reviewed. Exact role trust requires sts:AssumeRole and sts:TagSession; PassRole uses iam:PassedToService lambda.amazonaws.com, and conditional grants from iam:AssociatedResourceArn stay unresolved without its actual request value. A recorded CREATED or UPDATED customer image with an active version must be covered by both RunMicrovm and CreateMicrovmShellAuthToken in one Region. PassNetworkConnector has no resource-level scope: authorization now uses a literal resource-less request with requested Region, preventing ARN-scoped allows and denies from being misread. A possible AWS-managed base-image route remains unknown when broad image grants exist because the base-image inventory and runtime eligibility are not established; shell establishment and useful role action remain conditional. Five positive/negative tests in tests/test_peaso_privesc_lambda_microvm_connector.py pass; old binding and current manifest verified.</x:v>
+      </x:c>
+      <x:c r="O150" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -3865,10 +6389,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G151" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H151" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I151" s="6" t="str"/>
+      <x:c r="J151" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K151" s="6" t="str"/>
+      <x:c r="L151" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M151" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N151" s="6" t="str">
+        <x:v>Exact free new Lambda function, CreateFunction, AddPermission grant to source principal and function-bound PassRole checked. Explicit InvokeFunction denies in identity policy, permissions boundary and collected SCP prevent an edge; conditional deny downgrades confidence. Wrong grant principal, wrong associated function, occupied name, missing inventory and disjoint function tests pass. Execution, quotas and uncollected session controls remain conditional; tests/test_peaso_privesc_aws_followups.py; AWS AddPermission, Lambda resource-policy and IAM policy evaluation docs.</x:v>
+      </x:c>
+      <x:c r="O151" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -3889,10 +6430,27 @@
         <x:v>tests/test_peaso_privesc_lambda_existing_sqs_mapping.py</x:v>
       </x:c>
       <x:c r="G152" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_existing_sqs_mapping.py</x:v>
       </x:c>
       <x:c r="H152" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_existing_sqs_mapping.py</x:v>
+      </x:c>
+      <x:c r="I152" s="6" t="str"/>
+      <x:c r="J152" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K152" s="6" t="str"/>
+      <x:c r="L152" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M152" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N152" s="6" t="str">
+        <x:v>Current audit: AWS Lambda CreateEventSourceMapping and SQS event-source, role-policy and KMS docs reviewed. The old generic requirement of PassRole, CreateFunction and CreateEventSourceMapping alone could report a role edge without any usable source. The evaluator now reports a conditional edge only for a collected same-Region SQS queue with usable visibility timeout, source SendMessage, role ReceiveMessage/DeleteMessage/GetQueueAttributes, a free function name covered by CreateFunction, function-bound PassRole, and resource-less CreateEventSourceMapping with lambda:FunctionArn for that function. Customer-managed KMS encryption and other poll-based sources remain unresolved rather than producing a definite edge; existing traffic without SendMessage remains possible and unresolved. Positive, absent send/read, wrong mapping function, encrypted and zero-visibility cases pass in tests/test_peaso_privesc_lambda_existing_sqs_mapping.py. Actual mapping and message processing remain conditional; exact prior binding and current manifest verified.</x:v>
+      </x:c>
+      <x:c r="O152" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -3913,10 +6471,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G153" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H153" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I153" s="6" t="str"/>
+      <x:c r="J153" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K153" s="6" t="str"/>
+      <x:c r="L153" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M153" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N153" s="6" t="str">
+        <x:v>Current audit: AWS Lambda CreateEventSourceMapping, DynamoDB Streams, DynamoDB stream-role policy and Service Authorization Reference docs reviewed. The former positive fixture lacked every stream-read grant, so the YAML now requires a source-and-role precondition. The evaluator joins one unused DynamoDB table name and one unused Lambda function name in the same collected Region; CreateTable and PutItem on the table; DescribeStream, GetShardIterator, GetRecords and resource-less ListStreams on the passed role; exact function CreateFunction and PassRole with iam:AssociatedResourceArn; and resource-less CreateEventSourceMapping with lambda:FunctionArn equal to that function. The new table can enable Streams on creation and the caller can write an item; the mapping defaults to enabled. Missing inventory, conditional authorization, or an unpredictable stream-version policy stays unknown. Positive, missing PutItem, missing role reads, missing ListStreams, missing inventory, disjoint table and wrong function condition cases pass in tests/test_peaso_privesc_aws_followups.py. Actual creation, polling and role action remain conditional; exact previous binding and current manifest verified.</x:v>
+      </x:c>
+      <x:c r="O153" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -3937,10 +6512,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G154" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H154" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I154" s="6" t="str"/>
+      <x:c r="J154" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K154" s="6" t="str"/>
+      <x:c r="L154" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M154" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N154" s="6" t="str">
+        <x:v>Current audit: AWS PutRule, PutTargets, EventBridge IAM conditions and Lambda AddPermission docs confirm a newly created default-bus rule is enabled by default, may combine ScheduleExpression and EventPattern, and can invoke a same-Region Lambda target with a resource-policy grant. The evaluator joins one free function, one free default-bus rule, exact PassRole with iam:AssociatedResourceArn, AddPermission with events.amazonaws.com, PutRule schedule context, and PutTargets with events:TargetArn equal to that function. TargetArn constrained to another function is rejected; a rule requiring events:source can still be scheduled when an event pattern supplies that source. Positive, disjoint Region, wrong PassRole association, wrong principal, occupied or managed rule, missing inventory, right/wrong target condition, and event-pattern condition cases pass in tests/test_peaso_privesc_aws_followups.py. Actual rule creation and invocation remain conditional; exact prior binding and current manifest verified.</x:v>
+      </x:c>
+      <x:c r="O154" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -3961,10 +6553,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G155" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H155" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I155" s="6" t="str"/>
+      <x:c r="J155" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K155" s="6" t="str"/>
+      <x:c r="L155" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M155" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N155" s="6" t="str">
+        <x:v>Exact free new function in valid partition Region, CreateFunction, CreateFunctionUrlConfig with AWS_IAM, InvokeFunctionUrl and InvokeFunction via URL on same function, Lambda role trust and function-bound PassRole checked. Wrong URL auth or associated ARN, occupied name and missing inventory negatives pass. Inline ZIP code supported; deployment and quota remain conditional; tests/test_peaso_privesc_aws_followups.py; AWS CreateFunction, FunctionCode, Function URL and IAM AssociatedResourceArn docs.</x:v>
+      </x:c>
+      <x:c r="O155" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -3985,10 +6594,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G156" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H156" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I156" s="6" t="str"/>
+      <x:c r="J156" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K156" s="6" t="str"/>
+      <x:c r="L156" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M156" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N156" s="6" t="str">
+        <x:v>Exact free new function in valid partition Region, CreateFunction and InvokeFunction on same function, Lambda role trust, and PassRole iam:PassedToService plus iam:AssociatedResourceArn bound to that function checked. Inline ZIP payload can be supplied directly to CreateFunction. Wrong association, disjoint names, occupied name and missing inventory negatives pass; second viable function remains reachable. Invocation and quota remain conditional; tests/test_peaso_privesc_aws_followups.py; AWS CreateFunction, FunctionCode and IAM AssociatedResourceArn docs.</x:v>
+      </x:c>
+      <x:c r="O156" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -4009,10 +6635,27 @@
         <x:v>tests/test_peaso_privesc_lambda_role_swap_wrapper.py</x:v>
       </x:c>
       <x:c r="G157" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_role_swap_wrapper.py</x:v>
       </x:c>
       <x:c r="H157" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_role_swap_wrapper.py</x:v>
+      </x:c>
+      <x:c r="I157" s="6" t="str"/>
+      <x:c r="J157" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K157" s="6" t="str"/>
+      <x:c r="L157" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M157" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N157" s="6" t="str">
+        <x:v>Current audit: AWS UpdateFunctionConfiguration, Lambda execution-wrapper, PublishLayerVersion and Service Authorization Reference docs reviewed. A full role edge still needs one collected active ZIP function with supported native runtime, completed update, free concurrency, no enforced code signing, exact configuration update and InvokeFunction, function-bound PassRole, and matching service trust. Chosen code can now come from UpdateFunctionCode or a new inline-published layer whose version the source may GetLayerVersion and attach while setting AWS_LAMBDA_EXEC_WRAPPER. The evaluator checks the same function and a publishable/readable layer; a customer KMS key or pre-existing controlled layer remains unresolved. Code-update positive, wrapper-only positive, missing layer read, disjoint layer, and KMS cases pass in tests/test_peaso_privesc_lambda_role_swap_wrapper.py. Runtime execution and role action remain conditional; exact prior binding and current manifest verified.</x:v>
+      </x:c>
+      <x:c r="O157" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -4031,10 +6674,29 @@
       <x:c r="E158" s="6" t="str"/>
       <x:c r="F158" s="6" t="str"/>
       <x:c r="G158" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
       </x:c>
       <x:c r="H158" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
+      </x:c>
+      <x:c r="I158" s="6" t="str"/>
+      <x:c r="J158" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K158" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
+      </x:c>
+      <x:c r="L158" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M158" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N158" s="6" t="str">
+        <x:v>Reviewed the HackTricks Cloud route against AWS Lambda resource-policy and IAM same-account evaluation documentation. A direct grant to a same-account IAM user can allow UpdateFunctionCode and InvokeFunction despite an implicit identity or boundary deny, while explicit identity, boundary or SCP denies still block it. The evaluator joins one collected active ZIP function to its execution role and verifies code signing, concurrency, exact PutResourcePolicy/AddPermission/RemovePermission grants, source-principal policy context and code/invoke denies; focused positive and negative cases cover wrong principal, disjoint function, identity/boundary/SCP denies, missing grants, inactive or Image functions and missing inventory. AWS applies different boundary and session-policy rules to role ARNs and assumed-role sessions; because the inventory does not identify an exact session principal and its session policy, this route remains UNKNOWN for role sources rather than claiming an executable escalation. AWS references: https://docs.aws.amazon.com/lambda/latest/dg/access-control-resource-based.html and https://docs.aws.amazon.com/IAM/latest/UserGuide/reference_policies_evaluation-logic_policy-eval-denyallow.html.</x:v>
+      </x:c>
+      <x:c r="O158" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -4053,10 +6715,27 @@
       <x:c r="E159" s="6" t="str"/>
       <x:c r="F159" s="6" t="str"/>
       <x:c r="G159" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="H159" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
+      </x:c>
+      <x:c r="I159" s="6" t="str"/>
+      <x:c r="J159" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K159" s="6" t="str"/>
+      <x:c r="L159" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M159" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N159" s="6" t="str">
+        <x:v>AWS Signer StartSigningJob and service authorization require an exact signing-profile ARN and expose signer:ProfileVersion; Lambda GetCodeSigningConfig authorizes the exact config ARN. The route joins one active ZIP function to its enforcing config and allowed active AWSLambda profile version, then checks scoped UpdateFunctionCode, GetCodeSigningConfig and StartSigningJob grants. A conditional role path additionally requires direct invocation and a same-Region, account-owned versioned S3 bucket with bucket-owner-enforced ownership, no unverified KMS/bucket-policy guard, source PutObject/GetObjectVersion/ListBucket and generated-prefix PutObject/GetObject authorization. Positive broad and narrow-prefix cases and wrong profile/version/config, canceled profile, suspended versioning, missing owner control, missing invoke or source-version read negatives pass directly; the profile collector retains only version/status/platform metadata, and old/current catalog binding is verified. Job completion and Lambda execution remain conditional. Existing controlled-object, cross-account profile, KMS and other trigger variants stay UNKNOWN unless their exact evidence is collected; they are not reported as definite failures.</x:v>
+      </x:c>
+      <x:c r="O159" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -4075,10 +6754,29 @@
       <x:c r="E160" s="6" t="str"/>
       <x:c r="F160" s="6" t="str"/>
       <x:c r="G160" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
       </x:c>
       <x:c r="H160" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
+      </x:c>
+      <x:c r="I160" s="6" t="str"/>
+      <x:c r="J160" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K160" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_lambda_code_update_paths.py</x:v>
+      </x:c>
+      <x:c r="L160" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M160" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N160" s="6" t="str">
+        <x:v>AWS UpdateFunctionCode accepts inline ZIP code and InvokeFunction runs the updated latest function. The evaluator now joins both grants on one collected active ZIP function, requires completed update, usable concurrency, a known unexpired runtime, unenforced code signing and Lambda role trust; missing invocation, image source, state, signing or trust evidence stays unknown. Focused positive and negative cases, strict catalog validation and syntax checks pass.</x:v>
+      </x:c>
+      <x:c r="O160" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -4099,10 +6797,29 @@
       </x:c>
       <x:c r="F161" s="6" t="str"/>
       <x:c r="G161" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_m2_role_effect.py</x:v>
       </x:c>
       <x:c r="H161" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_m2_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I161" s="6" t="str">
+        <x:v>tests/test_aws_m2_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J161" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K161" s="6" t="str"/>
+      <x:c r="L161" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M161" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N161" s="6" t="str">
+        <x:v>Current audit: AWS M2 CreateApplication and application-definition documentation confirm an engine-specific definition and application role are required. The evaluator retains the exact Available environment, generated application authorization, PassRole condition and S3 definition-access checks, then requires one fresh reviewed execution record naming the exact environment, application, RoleId and accepted source-controlled artifacts, successful deployment/start, and a useful role-only action. Missing, duplicate, mismatched, incomplete, stale and caller-already-authorized proofs stay unresolved or absent. Focused positive and negative proof tests pass; historical catalog binding and upstream synchronization verified.</x:v>
+      </x:c>
+      <x:c r="O161" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -4123,10 +6840,29 @@
       </x:c>
       <x:c r="F162" s="6" t="str"/>
       <x:c r="G162" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_mgh_automation_role_effect.py</x:v>
       </x:c>
       <x:c r="H162" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_mgh_automation_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I162" s="6" t="str">
+        <x:v>tests/test_aws_mgh_automation_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J162" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K162" s="6" t="str"/>
+      <x:c r="L162" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M162" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N162" s="6" t="str">
+        <x:v>Current audit: AWS Migration Hub Automation docs confirm the us-east-1 preview and home Region requirement, SSM/Lambda runtime target, service-role trust and four core permissions; the Service Authorization Reference confirms CreateAutomationUnit and CreateAutomationRun are resource-less and AssociateAutomationUnitRole is scoped to the exact unit ARN. The evaluator now requires one fresh reviewed run naming the exact created unit, associated RoleId, controlled runtime target and useful role-only action, plus current source Create/Associate/Run/PassRole and target-role action authorization. Missing, duplicate, stale, wrong-target and direct-caller proofs remain unresolved or absent. Focused positive and negative tests and historical binding pass.</x:v>
+      </x:c>
+      <x:c r="O162" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -4147,10 +6883,29 @@
       </x:c>
       <x:c r="F163" s="6" t="str"/>
       <x:c r="G163" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_orchestrator_role_effect.py</x:v>
       </x:c>
       <x:c r="H163" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_orchestrator_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I163" s="6" t="str">
+        <x:v>tests/test_aws_orchestrator_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J163" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K163" s="6" t="str"/>
+      <x:c r="L163" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M163" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N163" s="6" t="str">
+        <x:v>Current audit: AWS Migration Hub Orchestrator docs confirm only automated custom steps use a script, the workflow action pair applies to one workflow, and the step must select an EC2 target. The evaluator now requires one fresh reviewed execution naming the same workflow, step group, step, S3 script, online managed instance, exact instance-role ID and useful role-only action. Current workflow grants and source script write or a previously verified usable script remain required. Missing, duplicate, stale, wrong-target and direct-caller proofs remain unresolved or absent. Both create/start and update/retry positive and negative tests and historical binding pass.</x:v>
+      </x:c>
+      <x:c r="O163" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -4171,10 +6926,29 @@
       </x:c>
       <x:c r="F164" s="6" t="str"/>
       <x:c r="G164" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_mwaa_role_effect.py, tests/test_peaso_privesc_mwaa_existing_dag.py</x:v>
       </x:c>
       <x:c r="H164" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_mwaa_role_effect.py, tests/test_peaso_privesc_mwaa_existing_dag.py</x:v>
+      </x:c>
+      <x:c r="I164" s="6" t="str">
+        <x:v>tests/test_aws_mwaa_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J164" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K164" s="6" t="str"/>
+      <x:c r="L164" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M164" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N164" s="6" t="str">
+        <x:v>Current audit: AWS UpdateEnvironment supports changing ExecutionRoleArn and code paths; AWS DAG docs say DAG files are synced into the scheduler and workers, but file access alone does not prove parse or execution. The evaluator retains exact environment UpdateEnvironment, PassRole with service and associated resource, writable DAG object and execution-role read/list checks. A concrete role edge now requires fresh reviewed evidence of successful update, parsing and task execution for that exact object under the exact RoleId, plus a useful role-only action. Missing, duplicate, stale, mismatched and direct-caller proofs stay unresolved or absent; startup-script, plugin and Airflow-token alternatives remain unresolved. Focused proof tests, historical binding and upstream sync pass.</x:v>
+      </x:c>
+      <x:c r="O164" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -4195,10 +6969,27 @@
         <x:v>tests/test_peaso_privesc_mwaa_existing_dag.py</x:v>
       </x:c>
       <x:c r="G165" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_mwaa_existing_dag.py</x:v>
       </x:c>
       <x:c r="H165" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_mwaa_existing_dag.py</x:v>
+      </x:c>
+      <x:c r="I165" s="6" t="str"/>
+      <x:c r="J165" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K165" s="6" t="str"/>
+      <x:c r="L165" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M165" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N165" s="6" t="str">
+        <x:v>AWS GetEnvironment and DAG synchronization docs: a Python file in the exact configured DAG folder is copied to schedulers and workers. The evaluator binds one AVAILABLE collected environment's ExecutionRoleArn, SourceBucketArn and DagS3Path with source PutObject and that same role's ListBucket/GetObject; it accepts exact named .py keys as well as a generated key. Positive and wrong object, role, read/list, status and denied-inventory negatives pass in tests/test_peaso_privesc_mwaa_existing_dag.py. Runtime parse, S3 encryption and effective resource-policy behavior remain conditional.</x:v>
+      </x:c>
+      <x:c r="O165" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -4219,10 +7010,29 @@
       </x:c>
       <x:c r="F166" s="6" t="str"/>
       <x:c r="G166" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_mwaa_role_effect.py, tests/test_peaso_privesc_mwaa_serverless_slr_scope.py</x:v>
       </x:c>
       <x:c r="H166" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_mwaa_role_effect.py, tests/test_peaso_privesc_mwaa_serverless_slr_scope.py</x:v>
+      </x:c>
+      <x:c r="I166" s="6" t="str">
+        <x:v>tests/test_aws_mwaa_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J166" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K166" s="6" t="str"/>
+      <x:c r="L166" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M166" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N166" s="6" t="str">
+        <x:v>Current audit: AWS MWAA Serverless docs require a versioned private S3 definition bucket and execution role, and take a definition snapshot on creation; default networking and customer KMS/VPC settings vary. The evaluator retains free-name and generated-ID grants, role passing, logging and service-linked-role requirements. A concrete edge now requires fresh reviewed evidence that the exact source-controlled YAML was accepted, the generated workflow ran under the exact RoleId, and a useful role-only action succeeded. Missing, duplicate, stale, mismatched and direct-caller proofs stay unresolved or absent; optional network/encryption viability is represented by actual execution proof. Focused proof tests, historical binding and upstream sync pass.</x:v>
+      </x:c>
+      <x:c r="O166" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -4243,10 +7053,29 @@
       </x:c>
       <x:c r="F167" s="6" t="str"/>
       <x:c r="G167" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_org_created_member_role_effect.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H167" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_org_created_member_role_effect.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I167" s="6" t="str">
+        <x:v>tests/test_aws_org_created_member_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J167" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K167" s="6" t="str"/>
+      <x:c r="L167" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M167" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N167" s="6" t="str">
+        <x:v>Current audit: AWS Organizations CreateAccount is asynchronous; a successful API return does not prove activation, and the new account access role may use a caller-chosen name. Existing source-management-account, wildcard new-role assume grant, root SCP, target RCP and org trust checks remain. A concrete edge now also requires one fresh reviewed CreateAccount SUCCEEDED record, active new account at the root, collected exact new access-role and target-role IDs, successful source assumption of the new role and target role, and a useful target-role action unavailable directly to the source. Missing, duplicate, stale, failed and wrong-account proofs stay unresolved or absent. Focused proof tests and historical binding pass.</x:v>
+      </x:c>
+      <x:c r="O167" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -4266,11 +7095,26 @@
       <x:c r="F168" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G168" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G168" s="6" t="str"/>
       <x:c r="H168" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I168" s="6" t="str"/>
+      <x:c r="J168" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K168" s="6" t="str"/>
+      <x:c r="L168" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M168" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N168" s="6" t="str">
+        <x:v>Exact member role trust and sts:AssumeRole authorization joined to the collected organization management account and an operational member state. ACTIVE and still-functional PENDING_CLOSURE are accepted; SUSPENDED, absent member, and non-management source are excluded. Role authority is described as its actual permissions, not assumed administrator access. Positive and negative regression in tests/test_peaso_privesc_schema_ext.py; AWS Organizations member-account access and account-state docs.</x:v>
+      </x:c>
+      <x:c r="O168" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -4289,10 +7133,27 @@
       <x:c r="E169" s="6" t="str"/>
       <x:c r="F169" s="6" t="str"/>
       <x:c r="G169" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="H169" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
+      </x:c>
+      <x:c r="I169" s="6" t="str"/>
+      <x:c r="J169" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K169" s="6" t="str"/>
+      <x:c r="L169" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M169" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N169" s="6" t="str">
+        <x:v>AWS RegisterUser API permits UserName, binds IamArn to an IAM user and says SessionName is unnecessary for IAM users; the QuickSight service authorization reference scopes RegisterUser to a user ARN and exposes IamArn/SessionName condition keys. An AWS ListUsers example shows user/default/&lt;name&gt; and federated/iam/&lt;IAM UserId&gt;, supporting the explicit UserName=source IAM username request. The evaluator requires a collected active IAM-compatible subscription, complete existing-user inventory without a username or immutable IAM UserId collision, exact source-bound IamArn, absent SessionName and RegisterUser on the chosen new user ARN. Focused positive, exact/narrow/wrong-resource, wrong identity/session, incompatible subscription, collision and denied-inventory tests pass. IAM-role registration is a distinct session-bound candidate in additional-technique-status.tsv; this sign-off covers only the IAM-user route. The accessible customer account had no QuickSight subscription in the queried Regions, so no live registration was performed.</x:v>
+      </x:c>
+      <x:c r="O169" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -4311,10 +7172,27 @@
       <x:c r="E170" s="6" t="str"/>
       <x:c r="F170" s="6" t="str"/>
       <x:c r="G170" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H170" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I170" s="6" t="str"/>
+      <x:c r="J170" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K170" s="6" t="str"/>
+      <x:c r="L170" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M170" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N170" s="6" t="str">
+        <x:v>Current audit confirms UpdateUser can promote an existing QuickSight IAM identity only when immutable PrincipalId exactly matches source IAM UserId, account subscription supports IAM sign-in, user is active and non-admin without custom permission restriction, and effective IAM permission covers the exact QuickSight user ARN. Positive and negative tests cover mismatched identity/resource, inactive or native user, existing ADMIN, custom permissions and incompatible subscription. AWS UpdateUser API, QuickSight User PrincipalId example and service authorization reference.</x:v>
+      </x:c>
+      <x:c r="O170" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -4335,10 +7213,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G171" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_rolesanywhere_global_create.py</x:v>
       </x:c>
       <x:c r="H171" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_rolesanywhere_global_create.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I171" s="6" t="str"/>
+      <x:c r="J171" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K171" s="6" t="str"/>
+      <x:c r="L171" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M171" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N171" s="6" t="str">
+        <x:v>CreateTrustAnchor and CreateProfile require a global Resource grant and are checked with exact requested Region, a target-scoped iam:PassRole, collected per-Region anchor/profile capacity, and trust for sts:AssumeRole, sts:TagSession, and sts:SetSourceIdentity on a new anchor. Unconditional or broad ArnLike trust-anchor SourceArn is accepted; exact existing SourceArn, wrong PassedToService, missing trust action, missing inventory, and wrong requested Region do not become positive. Focused positive/negative regression in tests/test_peaso_privesc_schema_ext.py; AWS Roles Anywhere CreateProfile/CreateTrustAnchor APIs, service authorization reference, trust model, and quotas.</x:v>
+      </x:c>
+      <x:c r="O171" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -4359,10 +7254,27 @@
         <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="G172" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="H172" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
+      </x:c>
+      <x:c r="I172" s="6" t="str"/>
+      <x:c r="J172" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K172" s="6" t="str"/>
+      <x:c r="L172" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M172" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N172" s="6" t="str">
+        <x:v>UpdateTrustAnchor now joins an exact writable enabled CERTIFICATE_BUNDLE trust anchor to an enabled same-Region profile listing the role, and evaluates the role trust for that anchor with sts:AssumeRole, sts:TagSession, and sts:SetSourceIdentity. AWS_ACM_PCA anchors cannot have their CA replaced; mismatched anchor/Region, disabled resources, missing trust action, explicit trust Deny, and restrictive profile session policies do not produce full-role paths. Positive and negative cases pass in tests/test_peaso_privesc_aws_ext_facts.py; AWS Roles Anywhere trust model, profile detail, UpdateTrustAnchor API, and getting-started guide.</x:v>
+      </x:c>
+      <x:c r="O172" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -4383,10 +7295,27 @@
         <x:v>tests/test_peaso_privesc_aws_s3_access_grants.py</x:v>
       </x:c>
       <x:c r="G173" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_s3_access_grants.py</x:v>
       </x:c>
       <x:c r="H173" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_s3_access_grants.py</x:v>
+      </x:c>
+      <x:c r="I173" s="6" t="str"/>
+      <x:c r="J173" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K173" s="6" t="str"/>
+      <x:c r="L173" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M173" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N173" s="6" t="str">
+        <x:v>S3 Access Grants location, IAM PassRole, grant, and GetDataAccess authorization targets, service principal, exact source-grantee and bounded READ session checked; both AWS-documented grant and location ARN forms, Region/partition joins, missing/duplicate evidence, wrong resource and condition negatives; tests/test_peaso_privesc_aws_s3_access_grants.py; AWS S3 Service Authorization Reference, Register a location, Create grants, and IAM PassedToService guide</x:v>
+      </x:c>
+      <x:c r="O173" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -4407,10 +7336,27 @@
         <x:v>tests/test_peaso_privesc_aws_s3_self_grant.py</x:v>
       </x:c>
       <x:c r="G174" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_s3_self_grant.py</x:v>
       </x:c>
       <x:c r="H174" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_s3_self_grant.py</x:v>
+      </x:c>
+      <x:c r="I174" s="6" t="str"/>
+      <x:c r="J174" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K174" s="6" t="str"/>
+      <x:c r="L174" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M174" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N174" s="6" t="str">
+        <x:v>Same-account bucket owner, exact source user or role, PutBucketPolicy on bucket ARN, accepted GetObject policy on bound prefix, prior denial, effective new read and guardrail review checked; partition mismatch, missing/duplicate evidence and nonwriter negatives; tests/test_peaso_privesc_aws_s3_self_grant.py; AWS S3 Access control and Required permissions for S3 API operations</x:v>
+      </x:c>
+      <x:c r="O174" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -4429,10 +7375,27 @@
       <x:c r="E175" s="6" t="str"/>
       <x:c r="F175" s="6" t="str"/>
       <x:c r="G175" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_lcc_attach.py</x:v>
       </x:c>
       <x:c r="H175" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_lcc_attach.py</x:v>
+      </x:c>
+      <x:c r="I175" s="6" t="str"/>
+      <x:c r="J175" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K175" s="6" t="str"/>
+      <x:c r="L175" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M175" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N175" s="6" t="str">
+        <x:v>AWS SageMaker lifecycle documentation confirms a notebook OnStart script executes with its execution-role credentials on a later start. The route joins an exact notebook and role, SageMaker trust, AL2023 platform, Stopped state or effective StopNotebookInstance, exact UpdateNotebookInstance and CreateNotebookInstanceLifecycleConfig grants, and complete inventory proving a valid free configuration name in the same Region. Focused positive and occupied-name, denied or malformed inventory, wrong notebook, role, trust, state, platform, permission and Region negatives pass. The published customer-role template now includes the reviewed sagemaker:ListNotebookInstanceLifecycleConfigs read; every managed policy fits the 6144-character IAM limit, and the previous template action set is preserved. Actual future start remains conditional; prior catalog binding is retained.</x:v>
+      </x:c>
+      <x:c r="O175" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -4451,10 +7414,27 @@
       <x:c r="E176" s="6" t="str"/>
       <x:c r="F176" s="6" t="str"/>
       <x:c r="G176" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_studio_lcc.py</x:v>
       </x:c>
       <x:c r="H176" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_studio_lcc.py</x:v>
+      </x:c>
+      <x:c r="I176" s="6" t="str"/>
+      <x:c r="J176" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K176" s="6" t="str"/>
+      <x:c r="L176" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M176" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N176" s="6" t="str">
+        <x:v>Verified the Studio profile route against AWS CreateStudioLifecycleConfig, UpdateUserProfile, CreateApp and Service Authorization Reference. The evaluator joins the exact profile execution role, IAM domain, an unused compatible profile app, a free lifecycle configuration name and scoped CreateStudioLifecycleConfig, UpdateUserProfile, CreateApp and AddTags grants with SageMaker trust. Incomplete inventories or guardrails remain unresolved; launch is conditional. Positive and negative direct tests cover wrong role, profile state, SSO domain, denied inventory, existing app, occupied name, missing AddTags and mismatched lifecycle ARN condition. The customer role includes ListStudioLifecycleConfigs without exceeding IAM policy limits; historical catalog binding verified.</x:v>
+      </x:c>
+      <x:c r="O176" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -4475,10 +7455,27 @@
         <x:v>tests/test_peaso_collectors_aws_ext.py, tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="G177" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_ext_facts.py</x:v>
       </x:c>
       <x:c r="H177" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_collectors_aws_ext.py, tests/test_peaso_privesc_aws_ext_facts.py</x:v>
+      </x:c>
+      <x:c r="I177" s="6" t="str"/>
+      <x:c r="J177" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K177" s="6" t="str"/>
+      <x:c r="L177" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M177" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N177" s="6" t="str">
+        <x:v>Exact collected user profile ARN, effective profile or domain-default execution role, InService profile/domain, IAM AuthMode, and an InService code app or same-profile CreateApp plus AddTags are joined before a conditional role path. Existing app, create-app, missing AddTags, wrong space, SSO mode, failed profile, deleting domain, and mismatched domain cases pass in tests/test_peaso_privesc_aws_ext_facts.py; domain-default collector case in tests/test_peaso_collectors_aws_ext.py. AWS CreatePresignedDomainUrl API and SageMaker authorization reference support the IAM-only URL and CreateApp dependent AddTags action.</x:v>
+      </x:c>
+      <x:c r="O177" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -4498,11 +7495,26 @@
       <x:c r="F178" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G178" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G178" s="6" t="str"/>
       <x:c r="H178" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I178" s="6" t="str"/>
+      <x:c r="J178" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K178" s="6" t="str"/>
+      <x:c r="L178" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M178" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N178" s="6" t="str">
+        <x:v>CreatePresignedNotebookInstanceUrl is checked on an exact collected notebook ARN joined to its RoleArn. InService produces a conditional role path; Stopped requires exact StartNotebookInstance permission and a restartable platform. Stopped AL2 and missing platform are excluded or unresolved under current SageMaker support; own-role self edge is suppressed. Positive and negative cases pass in tests/test_peaso_privesc_schema_ext.py; AWS CreatePresignedNotebookInstanceUrl API and SageMaker AL2 notebook lifecycle docs.</x:v>
+      </x:c>
+      <x:c r="O178" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -4521,10 +7533,27 @@
       <x:c r="E179" s="6" t="str"/>
       <x:c r="F179" s="6" t="str"/>
       <x:c r="G179" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_new_profile.py</x:v>
       </x:c>
       <x:c r="H179" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_new_profile.py</x:v>
+      </x:c>
+      <x:c r="I179" s="6" t="str"/>
+      <x:c r="J179" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K179" s="6" t="str"/>
+      <x:c r="L179" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M179" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N179" s="6" t="str">
+        <x:v>AWS CreateUserProfile, UserSettings, CreatePresignedDomainUrl and Service Authorization Reference confirm an explicit UserSettings.ExecutionRole, IAM-only URL access, user-profile and app ARN scopes, iam:PassedToService=sagemaker.amazonaws.com and dependent AddTags. The route now joins an InService IAM domain, complete profile-name inventory and a free valid name, exact scoped CreateUserProfile, CreatePresignedDomainUrl, CreateApp, app AddTags and PassRole grants, plus SageMaker service trust. Profile creation, app startup and URL access remain conditional; incomplete inventories and guardrails remain unknown. Direct positive and negative tests cover scoped permissions, missing app tagging permission, wrong app, wrong domain/auth/state, denied inventory, occupied name, wrong PassRole service and wrong trust. Previous catalog binding is retained.</x:v>
+      </x:c>
+      <x:c r="O179" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -4543,10 +7572,27 @@
       <x:c r="E180" s="6" t="str"/>
       <x:c r="F180" s="6" t="str"/>
       <x:c r="G180" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H180" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I180" s="6" t="str"/>
+      <x:c r="J180" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K180" s="6" t="str"/>
+      <x:c r="L180" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M180" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N180" s="6" t="str">
+        <x:v>AWS CreateHyperParameterTuningJob and HyperParameterTrainingJobDefinition docs confirm a caller-selected tuning-job ARN, required OutputDataConfig, optional input channels and script-mode StaticHyperParameters. The AWS SageMaker training toolkit consumes sagemaker_program and sagemaker_submit_directory; HPO does not expose inline ContainerEntrypoint. The current route joins a complete regional tuning-job inventory and free valid name, exact CreateHyperParameterTuningJob and PassRole grants, service trust, a same-Region bucket with complete policy/encryption details, direct source PutObject and target-role GetObject on one code archive, and an unconditional target-role PutObject grant covering the generated child jobs output prefix. Managed image availability, instance capacity and successful child-job startup remain conditional. Positive scoped-grant and missing code upload/read/output, occupied name, denied inventory, wrong Region, SSE-KMS, bucket deny, wrong PassRole service and forced network isolation negatives pass; old catalog binding is retained. Complex or external S3 paths remain UNKNOWN rather than claiming no route.</x:v>
+      </x:c>
+      <x:c r="O180" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -4565,10 +7611,29 @@
       <x:c r="E181" s="6" t="str"/>
       <x:c r="F181" s="6" t="str"/>
       <x:c r="G181" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_new_workload_role_paths.py</x:v>
       </x:c>
       <x:c r="H181" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_new_workload_role_paths.py</x:v>
+      </x:c>
+      <x:c r="I181" s="6" t="str"/>
+      <x:c r="J181" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K181" s="6" t="str">
+        <x:v>tests/test_peaso_privesc_new_workload_role_paths.py</x:v>
+      </x:c>
+      <x:c r="L181" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="M181" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N181" s="6" t="str">
+        <x:v>Verified SageMaker API, authorization resource scope and optional dependencies; same unused notebook ARN required for create and URL, with exact PassRole and service trust; scoped and broad policy regression cases pass</x:v>
+      </x:c>
+      <x:c r="O181" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -4587,10 +7652,27 @@
       <x:c r="E182" s="6" t="str"/>
       <x:c r="F182" s="6" t="str"/>
       <x:c r="G182" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H182" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I182" s="6" t="str"/>
+      <x:c r="J182" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K182" s="6" t="str"/>
+      <x:c r="L182" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M182" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N182" s="6" t="str">
+        <x:v>AWS CreateProcessingJob and Service Authorization docs confirm a caller-selected processing-job ARN, optional S3 inputs/outputs, the iam:PassRole dependency and NetworkIsolation/InstanceTypes condition keys. The Processing job AppSpecification supports an inline entrypoint, and SageMaker-managed images use service-owned pull credentials. Current evaluator requires complete regional job-name inventory, a free valid name, exact CreateProcessingJob grant for a non-isolated CPU instance, exact PassRole with iam:PassedToService, compatible service trust and known guardrails. It reports a conditional edge because image availability, capacity and successful startup remain unobserved. Positive scoped-job and negative occupied-name, denied-inventory, wrong-service and isolation-condition tests pass; previous catalog binding is preserved.</x:v>
+      </x:c>
+      <x:c r="O182" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -4609,10 +7691,27 @@
       <x:c r="E183" s="6" t="str"/>
       <x:c r="F183" s="6" t="str"/>
       <x:c r="G183" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H183" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I183" s="6" t="str"/>
+      <x:c r="J183" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K183" s="6" t="str"/>
+      <x:c r="L183" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M183" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N183" s="6" t="str">
+        <x:v>AWS CreateTrainingJob documentation confirms caller-supplied ContainerEntrypoint and ContainerArguments, a required S3OutputPath, and a caller-selected job name; AWS prebuilt images use service-owned pull credentials. Current evaluator joins a complete regional training-job inventory and free valid name, exact CreateTrainingJob and PassRole grants, SageMaker service trust, network isolation off and a same-Region existing bucket whose output object the passed role can write. It excludes buckets with unresolved policy or encryption details, or default SSE-KMS without a proven KMS path. The role edge remains conditional on a compatible image, available instance and successful startup. Positive scoped job plus missing or bucket-policy-only output grant, empty or denied bucket inventory, occupied name, wrong Region, KMS, bucket deny and isolation-condition negatives pass; previous catalog binding is retained.</x:v>
+      </x:c>
+      <x:c r="O183" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -4633,10 +7732,29 @@
       </x:c>
       <x:c r="F184" s="6" t="str"/>
       <x:c r="G184" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_sagemaker_hyperpod_role_effect.py</x:v>
       </x:c>
       <x:c r="H184" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_sagemaker_hyperpod_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I184" s="6" t="str">
+        <x:v>tests/test_aws_sagemaker_hyperpod_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J184" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K184" s="6" t="str"/>
+      <x:c r="L184" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M184" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N184" s="6" t="str">
+        <x:v>Current audit: AWS HyperPod docs say UpdateClusterSoftware cannot switch Slurm groups from the default AMI to custom, but can patch between custom AMIs; DescribeCluster identifies each group execution role and image. Collector now retains ImageId. The evaluator binds one InService cluster and exact instance group/role, rejects a Slurm transition lacking a prior custom AMI, and requires fresh reviewed evidence that a same-account unencrypted single-volume compatible controlled AMI was applied, nodes booted its startup code and a useful role-only action succeeded. Current UpdateClusterSoftware and role permissions are checked. Missing, duplicate, stale, unsupported-transition and direct-caller proofs stay unresolved or absent. Focused proof tests and historical binding pass.</x:v>
+      </x:c>
+      <x:c r="O184" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -4655,10 +7773,27 @@
       <x:c r="E185" s="6" t="str"/>
       <x:c r="F185" s="6" t="str"/>
       <x:c r="G185" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_new_profile.py</x:v>
       </x:c>
       <x:c r="H185" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_new_profile.py</x:v>
+      </x:c>
+      <x:c r="I185" s="6" t="str"/>
+      <x:c r="J185" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K185" s="6" t="str"/>
+      <x:c r="L185" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M185" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N185" s="6" t="str">
+        <x:v>HackTricks Cloud UpdateDomain procedure, AWS UpdateDomain/CreateUserProfile APIs and SageMaker authorization reference confirm that changing DefaultUserSettings.ExecutionRole then creating a profile without an explicit override can inherit the passed role. The evaluator joins an InService IAM domain, a complete domain app inventory with no existing app, a free valid profile name, exact scoped UpdateDomain, CreateUserProfile, CreateApp, CreatePresignedDomainUrl, app AddTags and SageMaker PassRole grants, and target service trust. Domains with existing apps or incomplete inventory stay unresolved; domain update, profile creation, app start and URL access remain conditional. Scoped positive and missing update, denied inventory, SSO/failed domain, same-domain app, malformed app, different-domain app and wrong app negatives pass. Previous catalog binding is retained.</x:v>
+      </x:c>
+      <x:c r="O185" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -4677,10 +7812,27 @@
       <x:c r="E186" s="6" t="str"/>
       <x:c r="F186" s="6" t="str"/>
       <x:c r="G186" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_lcc_update.py</x:v>
       </x:c>
       <x:c r="H186" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_lcc_update.py</x:v>
+      </x:c>
+      <x:c r="I186" s="6" t="str"/>
+      <x:c r="J186" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K186" s="6" t="str"/>
+      <x:c r="L186" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M186" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N186" s="6" t="str">
+        <x:v>AWS API documentation confirms the attached OnStart script runs at the next start with root and notebook execution-role privileges. Exact collected notebook/configuration/role and service-trust joins, scoped update permission, and positive and negative evaluator tests verified. Future restart is conditional.</x:v>
+      </x:c>
+      <x:c r="O186" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -4699,10 +7851,27 @@
       <x:c r="E187" s="6" t="str"/>
       <x:c r="F187" s="6" t="str"/>
       <x:c r="G187" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_role_swap.py</x:v>
       </x:c>
       <x:c r="H187" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_sagemaker_role_swap.py</x:v>
+      </x:c>
+      <x:c r="I187" s="6" t="str"/>
+      <x:c r="J187" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K187" s="6" t="str"/>
+      <x:c r="L187" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M187" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N187" s="6" t="str">
+        <x:v>AWS UpdateUserProfile and execution-role documentation confirm that a profile role can be changed, while the Service Authorization Reference binds UpdateUserProfile and CreatePresignedDomainUrl to one user-profile ARN, CreateApp to one app ARN and PassRole to SageMaker. The evaluator now joins an InService profile and IAM domain, complete app inventory with no existing profile app, exact scoped UpdateUserProfile, CreatePresignedDomainUrl, CreateApp, app AddTags and PassRole grants, and target service trust. Existing apps remain unresolved pending a separate state/restart analysis; update, app start and URL access remain conditional. Scoped positive and wrong profile, app, auth, state, trust, PassRole service, denied inventories, existing app and multiple-profile negatives pass. Historical catalog binding is retained.</x:v>
+      </x:c>
+      <x:c r="O187" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -4723,10 +7892,27 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G188" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_scheduler_update_20261022.py</x:v>
       </x:c>
       <x:c r="H188" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_scheduler_update_20261022.py</x:v>
+      </x:c>
+      <x:c r="I188" s="6" t="str"/>
+      <x:c r="J188" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K188" s="6" t="str"/>
+      <x:c r="L188" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M188" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N188" s="6" t="str">
+        <x:v>Replaced the generic passed-role edge with a concrete IAM inline-policy self-grant. A same-account IAM user or role must be able to create an exact default-group schedule, pass an exact Scheduler-trusting role with iam:PassedToService, and that role must have effective PutUserPolicy or PutRolePolicy on the source principal. The source must lack CreateUser beforehand and explicit denies, boundary and collected SCP controls must permit it after the policy write. Same-account schedule scope, missing role action, wrong role trust and SourceArn, wrong PassRole service, prior access and explicit deny negatives pass in tests/test_peaso_privesc_aws_followups.py. Actual schedule execution and inline-policy write remain conditional; other Scheduler target APIs remain separate unresolved variants; an existing-schedule UpdateSchedule self-grant is now cataloged separately. AWS Scheduler universal targets, schedule groups and IAM PutUserPolicy/PutRolePolicy docs.</x:v>
+      </x:c>
+      <x:c r="O188" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -4747,10 +7933,27 @@
         <x:v>tests/test_peaso_privesc_scheduler_update_20261022.py</x:v>
       </x:c>
       <x:c r="G189" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_scheduler_update_20261022.py</x:v>
       </x:c>
       <x:c r="H189" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_scheduler_update_20261022.py</x:v>
+      </x:c>
+      <x:c r="I189" s="6" t="str"/>
+      <x:c r="J189" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K189" s="6" t="str"/>
+      <x:c r="L189" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M189" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N189" s="6" t="str">
+        <x:v>Exact existing schedule ARN and AWS-owned encryption state are collected by ListSchedules/GetSchedule with a KMS provenance marker. A same-account IAM user or role must have UpdateSchedule on that ARN and iam:PassRole on an exact Scheduler-trusting role; that role must have PutUserPolicy or PutRolePolicy on the source. Before/after iam:CreateUser checks reject prior permission, explicit denies and blocking guardrails. Positive and negative cases cover wrong ARN, incomplete schedule read, customer KMS key, missing KMS provenance, wrong action/trust and existing source grant in tests/test_peaso_privesc_scheduler_update_20261022.py; the scheduled write remains conditional. AWS UpdateSchedule, Scheduler IAM authorization and universal-target docs.</x:v>
+      </x:c>
+      <x:c r="O189" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -4771,10 +7974,27 @@
         <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="G190" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="H190" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
+      </x:c>
+      <x:c r="I190" s="6" t="str"/>
+      <x:c r="J190" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K190" s="6" t="str"/>
+      <x:c r="L190" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M190" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N190" s="6" t="str">
+        <x:v>Exact same-account IAM user, secret ARN, PutResourcePolicy, accepted self-naming policy, prior denial, new GetSecretValue and KMS decrypt checked; missing/duplicate/mismatched evidence and nonwriter negatives; tests/test_peaso_privesc_aws_scoped_grants.py; AWS Secrets Manager Service Authorization Reference and PutResourcePolicy API</x:v>
+      </x:c>
+      <x:c r="O190" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -4795,10 +8015,29 @@
       </x:c>
       <x:c r="F191" s="6" t="str"/>
       <x:c r="G191" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_servicecatalog_role_effect.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H191" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_servicecatalog_role_effect.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I191" s="6" t="str">
+        <x:v>tests/test_aws_servicecatalog_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J191" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K191" s="6" t="str"/>
+      <x:c r="L191" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M191" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N191" s="6" t="str">
+        <x:v>Current audit: AWS Service Catalog docs confirm launch constraints belong to specific product-portfolio associations. This variant requires source permission to associate itself with the exact portfolio and fresh reviewed evidence that association succeeded; the same record binds one owned product, its launch role, controlled new artifact, successful provisioning and useful role-only action under the exact RoleId. Current product and portfolio grants remain required. Missing, duplicate, stale, wrong-product/portfolio and direct-caller proofs stay unresolved or absent. Focused positive/negative tests and catalog binding pass.</x:v>
+      </x:c>
+      <x:c r="O191" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -4819,10 +8058,29 @@
       </x:c>
       <x:c r="F192" s="6" t="str"/>
       <x:c r="G192" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_servicecatalog_role_effect.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H192" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_servicecatalog_role_effect.py, tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I192" s="6" t="str">
+        <x:v>tests/test_aws_servicecatalog_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J192" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K192" s="6" t="str"/>
+      <x:c r="L192" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M192" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N192" s="6" t="str">
+        <x:v>Current audit: AWS Service Catalog docs confirm CreateProvisioningArtifact cannot modify a shared product and a launch constraint applies to a specific product in a portfolio. The evaluator now binds one owned product, portfolio, exact launch-constraint role and RoleId, source-controlled accepted new artifact, successful provisioning and useful role-only action using one fresh reviewed record. Current CreateProvisioningArtifact and ProvisionProduct grants on the product, prior portfolio end-user status and target-role action authorization are required. Missing, duplicate, stale, wrong-product/portfolio and direct-caller proofs stay unresolved or absent. Focused positive/negative tests and catalog binding pass.</x:v>
+      </x:c>
+      <x:c r="O192" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -4843,10 +8101,27 @@
         <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="G193" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
       </x:c>
       <x:c r="H193" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_scoped_grants.py</x:v>
+      </x:c>
+      <x:c r="I193" s="6" t="str"/>
+      <x:c r="J193" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K193" s="6" t="str"/>
+      <x:c r="L193" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M193" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N193" s="6" t="str">
+        <x:v>Exact existing Monitor portal, CreateAccessPolicy on portal ARN, IAM user identity, accepted ADMINISTRATOR policy, prior denial and effective new portal access checked; IAM role source excluded, missing/duplicate/mismatched evidence and nonwriter negatives; tests/test_peaso_privesc_aws_scoped_grants.py; AWS IoT SiteWise CreateAccessPolicy API and Service Authorization Reference</x:v>
+      </x:c>
+      <x:c r="O193" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -4866,11 +8141,26 @@
       <x:c r="F194" s="6" t="str">
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
-      <x:c r="G194" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G194" s="6" t="str"/>
       <x:c r="H194" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I194" s="6" t="str"/>
+      <x:c r="J194" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K194" s="6" t="str"/>
+      <x:c r="L194" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M194" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N194" s="6" t="str">
+        <x:v>Exact same-account IAM user and collected topic are joined by ARN. Effective SetTopicAttributes is required, prior Subscribe and surviving identity or boundary denies block the route; a replaceable topic-policy Deny does not. A direct user grant bypasses a boundary implicit deny; the target is only permission to request a subscription, not endpoint confirmation or message delivery. Focused positive and rejection tests pass in tests/test_peaso_privesc_aws_followups.py; AWS SNS resource-policy and IAM same-account authorization docs.</x:v>
+      </x:c>
+      <x:c r="O194" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -4890,11 +8180,26 @@
       <x:c r="F195" s="6" t="str">
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
-      <x:c r="G195" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G195" s="6" t="str"/>
       <x:c r="H195" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I195" s="6" t="str"/>
+      <x:c r="J195" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K195" s="6" t="str"/>
+      <x:c r="L195" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M195" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N195" s="6" t="str">
+        <x:v>Exact same-account IAM user and collected queue are joined by ARN and URL. Effective SetQueueAttributes is required; prior ReceiveMessage and surviving identity or boundary denies block the route. For SSE-KMS, an exact key ARN or ID must resolve to a collected regional key and policy with effective kms:Decrypt for the source; aliases and missing policies give no edge. A direct user queue-policy grant bypasses a boundary implicit deny but not an explicit deny; account-root delegation alone is not prior access. The target is only a new queue permission, not observed message access. Focused positive and negative tests pass in tests/test_peaso_privesc_aws_followups.py; AWS SQS key management and queue-policy docs.</x:v>
+      </x:c>
+      <x:c r="O195" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -4914,11 +8219,26 @@
       <x:c r="F196" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G196" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G196" s="6" t="str"/>
       <x:c r="H196" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I196" s="6" t="str"/>
+      <x:c r="J196" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K196" s="6" t="str"/>
+      <x:c r="L196" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M196" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N196" s="6" t="str">
+        <x:v>A running instance with the exact target instance-profile role must have an online SSM record from the same account and Region; CreateAssociation must cover a creatable association ARN and same-Region AWS shell document. The Targets form can name the instance ID without instance-resource authorization; association-only, document-only, non-shell document and wrong-Region grants do not form a concrete path. Execution and platform remain conditional; tests/test_peaso_privesc_schema_ext.py; AWS CreateAssociation API and Working with associations using IAM</x:v>
+      </x:c>
+      <x:c r="O196" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -4938,11 +8258,26 @@
       <x:c r="F197" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G197" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G197" s="6" t="str"/>
       <x:c r="H197" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I197" s="6" t="str"/>
+      <x:c r="J197" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K197" s="6" t="str"/>
+      <x:c r="L197" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M197" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N197" s="6" t="str">
+        <x:v>SSM-trusting same-account role and exact PassRole with iam:PassedToService, one creatable Automation document name and type in a Region, StartAutomationExecution on that document or definition plus a future execution ARN checked; mismatched create/start names, occupied name, wrong document type, and grants tied only to old execution IDs rejected. Execution effects remain conditional; tests/test_peaso_privesc_schema_ext.py; AWS Automation setup, StartAutomationExecution and PassRole troubleshooting guides</x:v>
+      </x:c>
+      <x:c r="O197" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -4963,10 +8298,27 @@
         <x:v>tests/test_peaso_privesc_incident_global_create.py, tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G198" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_incident_global_create.py</x:v>
       </x:c>
       <x:c r="H198" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_incident_global_create.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I198" s="6" t="str"/>
+      <x:c r="J198" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K198" s="6" t="str"/>
+      <x:c r="L198" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M198" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N198" s="6" t="str">
+        <x:v>Active Incident Manager replication in the execution Region, global CreateResponsePlan grant, exact Regionless response-plan ARN, creatable Automation document, CreateResponsePlan or UpdateResponsePlan and StartIncident on one plan, PassRole with iam:PassedToService=ssm-incidents.amazonaws.com, runbook role trust to that service, and role StartAutomationExecution on the new document and future execution checked. Wrong service trust, missing role execution grant, wrong document Region, wrong plan account or ARN shape and missing replication reject the path; tests/test_peaso_privesc_schema_ext.py and tests/test_peaso_privesc_incident_global_create.py; AWS CreateResponsePlan and Incident Manager runbook-role guides</x:v>
+      </x:c>
+      <x:c r="O198" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -4987,10 +8339,29 @@
       </x:c>
       <x:c r="F199" s="6" t="str"/>
       <x:c r="G199" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_ssm_jit_role_effect.py</x:v>
       </x:c>
       <x:c r="H199" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_ssm_jit_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I199" s="6" t="str">
+        <x:v>tests/test_aws_ssm_jit_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J199" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K199" s="6" t="str"/>
+      <x:c r="L199" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M199" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N199" s="6" t="str">
+        <x:v>Current audit: AWS SSM JIT docs confirm only STS AssumeRole requesters are supported, requests may need manual approval, GetAccessToken follows approval, and the token opens a session on the approved node. The evaluator retains the exact online managed instance and current StartAccessRequest/GetAccessToken grants, then requires one fresh reviewed record binding the exact requester session and RoleId, node, approved request and open window, issued token, established session, use of instance-role credentials and a useful role-only action. Missing, duplicate, expired, wrong-session and direct-caller proofs stay unresolved or absent. Focused positive/negative tests and historical binding pass.</x:v>
+      </x:c>
+      <x:c r="O199" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -5010,11 +8381,26 @@
       <x:c r="F200" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G200" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G200" s="6" t="str"/>
       <x:c r="H200" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I200" s="6" t="str"/>
+      <x:c r="J200" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K200" s="6" t="str"/>
+      <x:c r="L200" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M200" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N200" s="6" t="str">
+        <x:v>Existing enabled maintenance window with a scheduled run, SSM-trusting target role and exact PassRole with iam:PassedToService=ssm.amazonaws.com, one creatable Automation document in the window Region, and RegisterTask permission on the window or UpdateMaintenanceWindowTask on the window and an existing AUTOMATION task checked. Wrong task type, wrong passed service and wrong-Region document grant reject the path; execution remains conditional; tests/test_peaso_privesc_schema_ext.py; AWS Schedule automations with maintenance windows and RegisterTaskWithMaintenanceWindow API</x:v>
+      </x:c>
+      <x:c r="O200" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -5034,11 +8420,26 @@
       <x:c r="F201" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G201" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G201" s="6" t="str"/>
       <x:c r="H201" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I201" s="6" t="str"/>
+      <x:c r="J201" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K201" s="6" t="str"/>
+      <x:c r="L201" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M201" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N201" s="6" t="str">
+        <x:v>Running instance with the target instance-profile role and same-Region online SSM record, enabled maintenance window with next execution, and exact RegisterTask permission on that window or UpdateMaintenanceWindowTask on both the window and an existing RUN_COMMAND task checked; missing window, disabled window, wrong Region, missing task and wrong task type rejected. The task may name an instance ID directly; eventual execution remains conditional; tests/test_peaso_privesc_schema_ext.py; AWS RegisterTaskWithMaintenanceWindow and UpdateMaintenanceWindowTask APIs</x:v>
+      </x:c>
+      <x:c r="O201" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -5058,11 +8459,26 @@
       <x:c r="F202" s="6" t="str">
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
-      <x:c r="G202" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
-      </x:c>
+      <x:c r="G202" s="6" t="str"/>
       <x:c r="H202" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I202" s="6" t="str"/>
+      <x:c r="J202" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K202" s="6" t="str"/>
+      <x:c r="L202" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M202" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N202" s="6" t="str">
+        <x:v>CreateActivation on the account plus PassRole on the exact same-account role with iam:PassedToService=ssm.amazonaws.com and role trust to ssm.amazonaws.com checked; missing create, wrong passed service, wrong role and wrong trust reject the path. AWS documents that the returned activation code and ID register a node and that the node receives a session token using its assigned service role; registration and credential use remain conditional; tests/test_peaso_privesc_schema_ext.py; AWS CreateActivation and hybrid service-role guides</x:v>
+      </x:c>
+      <x:c r="O202" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -5083,10 +8499,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G203" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_audit_fixes.py, tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
       </x:c>
       <x:c r="H203" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_audit_fixes.py, tests/test_peaso_privesc_schema_ext.py, tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
+      </x:c>
+      <x:c r="I203" s="6" t="str"/>
+      <x:c r="J203" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K203" s="6" t="str"/>
+      <x:c r="L203" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M203" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N203" s="6" t="str">
+        <x:v>Running instance with exact instance-profile role, recorded online SSM state in the same account and Region, and SendCommand grants for the instance and same-Region AWS shell document checked; wrong-region managed record, wrong-region or missing document, and missing ping status do not yield a concrete path. OS/document compatibility and access to role credentials remain conditional; tests/test_peaso_privesc_schema_ext.py; AWS Run Command permissions guide</x:v>
+      </x:c>
+      <x:c r="O203" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -5107,10 +8540,27 @@
         <x:v>tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
       </x:c>
       <x:c r="G204" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
       </x:c>
       <x:c r="H204" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
+      </x:c>
+      <x:c r="I204" s="6" t="str"/>
+      <x:c r="J204" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K204" s="6" t="str"/>
+      <x:c r="L204" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M204" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N204" s="6" t="str">
+        <x:v>A collected online mi- node's IamRole name must match the exact same-account target role, and SendCommand must cover both that node's managed-instance ARN and the platform-matching AWS shell document. Positive and wrong node, role, platform, document, offline and denied-inventory cases pass in tests/test_peaso_privesc_ssm_hybrid_shell.py. AWS InstanceInformation, hybrid role and root-level command docs support the join; actual command processing and credential access remain conditional.</x:v>
+      </x:c>
+      <x:c r="O204" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -5131,10 +8581,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G205" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
       </x:c>
       <x:c r="H205" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_schema_ext.py, tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
+      </x:c>
+      <x:c r="I205" s="6" t="str"/>
+      <x:c r="J205" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K205" s="6" t="str"/>
+      <x:c r="L205" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M205" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N205" s="6" t="str">
+        <x:v>Running instance with exact instance-profile role, recorded online SSM state in the same account and Region, StartSession on the instance and same-Region default shell document, and OpenDataChannel covering a future session in the instance account and Region checked; wrong-region managed record, wrong document, wrong account/Region channel, exact old session ARN and missing ping status rejected. Shell and channel details remain conditional; tests/test_peaso_privesc_schema_ext.py; AWS Session Manager default session document and access-policy examples</x:v>
+      </x:c>
+      <x:c r="O205" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -5155,10 +8622,27 @@
         <x:v>tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
       </x:c>
       <x:c r="G206" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
       </x:c>
       <x:c r="H206" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_ssm_hybrid_shell.py</x:v>
+      </x:c>
+      <x:c r="I206" s="6" t="str"/>
+      <x:c r="J206" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K206" s="6" t="str"/>
+      <x:c r="L206" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M206" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N206" s="6" t="str">
+        <x:v>A collected online mi- node's IamRole name must match the exact same-account target role, and StartSession must cover that node and its default shell document plus OpenDataChannel for a future session. Positive and wrong node, document, exact old channel, absent channel and denied-inventory cases pass in tests/test_peaso_privesc_ssm_hybrid_shell.py. AWS SSM InstanceInformation and session authorization docs support the join; live shell and local credential access remain conditional.</x:v>
+      </x:c>
+      <x:c r="O206" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -5179,10 +8663,27 @@
       </x:c>
       <x:c r="F207" s="6" t="str"/>
       <x:c r="G207" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H207" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I207" s="6" t="str"/>
+      <x:c r="J207" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K207" s="6" t="str"/>
+      <x:c r="L207" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M207" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N207" s="6" t="str">
+        <x:v>PassRole uses states.amazonaws.com; creation or update and execution are joined to one state machine. A concrete edge additionally needs one fresh reviewed SDK task on the current machine revision, exact target RoleId, successful useful action/resource allowed by the role but not the source. Positive and missing, stale, wrong-revision, wrong-role, wrong-action and direct-source-grant cases in test_peaso_privesc_aws_followups.py; previous catalog binding retained.</x:v>
+      </x:c>
+      <x:c r="O207" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -5203,10 +8704,27 @@
       </x:c>
       <x:c r="F208" s="6" t="str"/>
       <x:c r="G208" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H208" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I208" s="6" t="str"/>
+      <x:c r="J208" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K208" s="6" t="str"/>
+      <x:c r="L208" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M208" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N208" s="6" t="str">
+        <x:v>Current audit: IAM PassRole to states.amazonaws.com and states:TestState are required. A concrete edge now needs one fresh reviewed unmocked TestState call for the exact role ID, supported action, resource, successful useful effect, and no direct caller grant. Missing, stale, duplicated, mocked, failed, wrong-role and already-directly-allowed witnesses stay unresolved. Positive, negative and historical-binding focused tests pass. AWS Step Functions TestState documentation.</x:v>
+      </x:c>
+      <x:c r="O208" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -5227,10 +8745,27 @@
       </x:c>
       <x:c r="F209" s="6" t="str"/>
       <x:c r="G209" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H209" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
+      </x:c>
+      <x:c r="I209" s="6" t="str"/>
+      <x:c r="J209" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K209" s="6" t="str"/>
+      <x:c r="L209" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M209" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N209" s="6" t="str">
+        <x:v>PassRole uses states.amazonaws.com; creation or update and execution are joined to one state machine. A concrete edge additionally needs one fresh reviewed SDK task on the current machine revision, exact target RoleId, successful useful action/resource allowed by the role but not the source. Positive and missing, stale, wrong-revision, wrong-role, wrong-action and direct-source-grant cases in test_peaso_privesc_aws_followups.py; previous catalog binding retained.</x:v>
+      </x:c>
+      <x:c r="O209" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -5251,10 +8786,27 @@
         <x:v>tests/test_peaso_privesc_schema_ext.py</x:v>
       </x:c>
       <x:c r="G210" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_coverage_references.py, tests/test_peaso_privesc_current_runtime_binding.py</x:v>
       </x:c>
       <x:c r="H210" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_coverage_references.py, tests/test_peaso_privesc_current_runtime_binding.py, tests/test_peaso_privesc_schema_ext.py</x:v>
+      </x:c>
+      <x:c r="I210" s="6" t="str"/>
+      <x:c r="J210" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K210" s="6" t="str"/>
+      <x:c r="L210" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M210" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N210" s="6" t="str">
+        <x:v>Exact target role trust, same-account direct principal grant without identity Allow, account-root trust requiring identity Allow, and explicit trust Deny checked; candidate indexing false negative corrected without sharing the grant with another principal; tests/test_peaso_privesc_schema_ext.py; AWS STS AssumeRole API and IAM role trust-policy guide</x:v>
+      </x:c>
+      <x:c r="O210" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -5275,10 +8827,29 @@
       </x:c>
       <x:c r="F211" s="6" t="str"/>
       <x:c r="G211" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_aws_workspaces_instances_role_effect.py</x:v>
       </x:c>
       <x:c r="H211" s="6" t="str">
-        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Unblock pytest import and run the full suite with this technique covered; Record the positive and negative test file for this technique</x:v>
+        <x:v>tests/test_aws_workspaces_instances_role_effect.py</x:v>
+      </x:c>
+      <x:c r="I211" s="6" t="str">
+        <x:v>tests/test_aws_workspaces_instances_role_effect.py</x:v>
+      </x:c>
+      <x:c r="J211" s="6" t="str">
+        <x:v>passed_normal_pytest</x:v>
+      </x:c>
+      <x:c r="K211" s="6" t="str"/>
+      <x:c r="L211" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M211" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N211" s="6" t="str">
+        <x:v>Current audit: AWS WorkSpaces Instances ManagedInstanceRequest supports an IAM instance profile and user data, while example IAM policies use ec2:RunInstances through aws:CalledVia=workspaces-instances.amazonaws.com. The evaluator now requires one fresh reviewed launch naming the exact profile and target RoleId, supported managed-instance configuration, controlled executed user data and a useful role-only action. It rechecks current CreateWorkspaceInstance, PassRole to ec2.amazonaws.com, service-linked role readiness and RunInstances on every recorded AMI/network/instance resource with CalledVia. Missing, duplicate, stale, wrong-profile/resource and direct-caller proofs stay unresolved or absent. Focused positive/negative tests and historical binding pass.</x:v>
+      </x:c>
+      <x:c r="O211" s="6" t="str">
+        <x:v>Resolve external evidence supply or mark the route manual; verify present and absent evidence end to end; Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -5299,16 +8870,33 @@
         <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="G212" s="6" t="str">
-        <x:v>blocked_before_collection</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
       </x:c>
       <x:c r="H212" s="6" t="str">
-        <x:v>Unblock pytest import and run the full suite with this technique covered</x:v>
+        <x:v>tests/test_peaso_privesc_aws_followups.py</x:v>
+      </x:c>
+      <x:c r="I212" s="6" t="str"/>
+      <x:c r="J212" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="K212" s="6" t="str"/>
+      <x:c r="L212" s="6" t="str">
+        <x:v>not_run_in_current_audit</x:v>
+      </x:c>
+      <x:c r="M212" s="6" t="str">
+        <x:v>static_parity_12145_passed_full_suite_stops_on_private_source_admission</x:v>
+      </x:c>
+      <x:c r="N212" s="6" t="str">
+        <x:v>Exact native GetCodeInterpreter role and READY interpreter joined to both StartCodeInterpreterSession and InvokeCodeInterpreter on one ARN. Positive, disjoint ARN, failed status and partial inventory regressions pass in tests/test_peaso_privesc_aws_followups.py; AWS GetCodeInterpreter and service authorization docs.</x:v>
+      </x:c>
+      <x:c r="O212" s="6" t="str">
+        <x:v>Audit exact positive and negative cases for this technique; reconcile merged private-source admission and rerun the full suite</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3239dbd09a04847"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce757a2640fb4111"/>
   </x:tableParts>
 </x:worksheet>
 </file>